--- a/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
+++ b/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:Y21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,57 +416,66 @@
         <v>Tipe Saluran</v>
       </c>
       <c r="E1" t="str">
+        <v>Tipe Simbol SLD</v>
+      </c>
+      <c r="F1" t="str">
         <v>Dari GI</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>Tipe Simbol Dari GI</v>
+      </c>
+      <c r="H1" t="str">
         <v>Tier Dari GI</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>Ke GI</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
+        <v>Tipe Simbol Ke GI</v>
+      </c>
+      <c r="K1" t="str">
         <v>Tier Ke GI</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>Tegangan</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>Jumlah Sirkit</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>No Sirkit</v>
       </c>
-      <c r="L1" t="str">
+      <c r="O1" t="str">
         <v>Status Operasi</v>
       </c>
-      <c r="M1" t="str">
+      <c r="P1" t="str">
         <v>Tingkat Kerawanan</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>Pembebanan Sirkit 1 (%)</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>Pembebanan Sirkit 2 (%)</v>
       </c>
-      <c r="P1" t="str">
+      <c r="S1" t="str">
         <v>Panjang Saluran (km)</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <v>Koridor / Wilayah</v>
       </c>
-      <c r="R1" t="str">
+      <c r="U1" t="str">
         <v>UIT</v>
       </c>
-      <c r="S1" t="str">
+      <c r="V1" t="str">
         <v>Kondisi / Permasalahan</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
         <v>Dampak</v>
       </c>
-      <c r="U1" t="str">
+      <c r="X1" t="str">
         <v>Mitigasi</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Y1" t="str">
         <v>Usulan / Solusi</v>
       </c>
     </row>
@@ -484,61 +493,70 @@
         <v>Bay IBT</v>
       </c>
       <c r="E2" t="str">
+        <v>IBT</v>
+      </c>
+      <c r="F2" t="str">
         <v>Suralaya Baru</v>
       </c>
-      <c r="F2">
+      <c r="G2" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="str">
         <v>500/150 kV</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" t="str">
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M2" t="str">
+      <c r="P2" t="str">
         <v>Sangat Rawan</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>88</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2">
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2">
         <v>0.5</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="T2" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R2" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S2" t="str">
+      <c r="U2" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V2" t="str">
         <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
       </c>
-      <c r="T2" t="str" xml:space="preserve">
+      <c r="W2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
 2. Pertumbuhan beban menjadi terhambat.
 3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
       </c>
-      <c r="U2" t="str" xml:space="preserve">
+      <c r="X2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
 2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW.
 3. Pemeliharaan IBT saat beban rendah.</v>
       </c>
-      <c r="V2" t="str" xml:space="preserve">
+      <c r="Y2" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
 Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025.</v>
       </c>
@@ -557,59 +575,68 @@
         <v>Bay IBT</v>
       </c>
       <c r="E3" t="str">
+        <v>IBT</v>
+      </c>
+      <c r="F3" t="str">
         <v>Suralaya</v>
       </c>
-      <c r="F3">
+      <c r="G3" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="str">
         <v>500/150 kV</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="str">
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M3" t="str">
+      <c r="P3" t="str">
         <v>Sangat Rawan</v>
       </c>
-      <c r="N3">
+      <c r="Q3">
         <v>84</v>
       </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3">
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3">
         <v>0.5</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="T3" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R3" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S3" t="str">
+      <c r="U3" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V3" t="str">
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
       </c>
-      <c r="T3" t="str" xml:space="preserve">
+      <c r="W3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
 2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
-      <c r="U3" t="str" xml:space="preserve">
+      <c r="X3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya.
 2. Pemeliharaan IBT saat beban rendah.</v>
       </c>
-      <c r="V3" t="str" xml:space="preserve">
+      <c r="Y3" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
 Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2026.</v>
       </c>
@@ -628,57 +655,66 @@
         <v>Bay IBT</v>
       </c>
       <c r="E4" t="str">
+        <v>IBT</v>
+      </c>
+      <c r="F4" t="str">
         <v>Cilegon Baru</v>
       </c>
-      <c r="F4">
+      <c r="G4" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>CLBRU</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
         <v>500/150 kV</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="str">
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M4" t="str">
+      <c r="P4" t="str">
         <v>Sangat Rawan</v>
       </c>
-      <c r="N4">
+      <c r="Q4">
         <v>76</v>
       </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4">
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4">
         <v>0.5</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="T4" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R4" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S4" t="str">
+      <c r="U4" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V4" t="str">
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama.</v>
       </c>
-      <c r="T4" t="str">
+      <c r="W4" t="str">
         <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
-      <c r="U4" t="str">
+      <c r="X4" t="str">
         <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
       </c>
-      <c r="V4" t="str" xml:space="preserve">
+      <c r="Y4" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
 Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA.</v>
       </c>
@@ -697,57 +733,66 @@
         <v>Bay Generator</v>
       </c>
       <c r="E5" t="str">
+        <v>Trafo Generator</v>
+      </c>
+      <c r="F5" t="str">
         <v>Unit 3</v>
       </c>
-      <c r="F5">
+      <c r="G5" t="str">
+        <v>Pembangkit</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" t="str">
         <v>500 kV</v>
       </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="str">
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M5" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N5">
+      <c r="P5" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q5">
         <v>60</v>
       </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5">
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5">
         <v>0.2</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="T5" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R5" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S5" t="str">
+      <c r="U5" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V5" t="str">
         <v>Evakuasi daya PLTU Suralaya Unit 3 (1. Pembangkit, 2. Trafo Step-Up, 3. CB).</v>
       </c>
-      <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str">
-        <v/>
-      </c>
-      <c r="V5" t="str">
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
         <v/>
       </c>
     </row>
@@ -759,63 +804,72 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>SUTT 150 kV SRLYA - SLRDA</v>
+        <v>Suralaya - Salira Indah (Sirkit 1)</v>
       </c>
       <c r="D6" t="str">
         <v>PHT</v>
       </c>
       <c r="E6" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F6" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
       <c r="G6" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="str">
         <v>SLRDA</v>
       </c>
-      <c r="H6">
+      <c r="J6" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K6">
         <v>2</v>
       </c>
-      <c r="I6" t="str">
+      <c r="L6" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6" t="str">
+      <c r="M6">
+        <v>2</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M6" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N6">
-        <v>54</v>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6">
-        <v>14.2</v>
-      </c>
-      <c r="Q6" t="str">
+      <c r="P6" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q6">
+        <v>52</v>
+      </c>
+      <c r="R6">
+        <v>48</v>
+      </c>
+      <c r="S6">
+        <v>12.5</v>
+      </c>
+      <c r="T6" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R6" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S6" t="str">
-        <v/>
-      </c>
-      <c r="T6" t="str">
-        <v/>
-      </c>
       <c r="U6" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V6" t="str">
+        <v/>
+      </c>
+      <c r="W6" t="str">
+        <v/>
+      </c>
+      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
         <v/>
       </c>
     </row>
@@ -827,63 +881,72 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>SUTT 150 kV SRLYA - PENDO</v>
+        <v>Suralaya - Salira Indah (Sirkit 2)</v>
       </c>
       <c r="D7" t="str">
         <v>PHT</v>
       </c>
       <c r="E7" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F7" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
       <c r="G7" t="str">
-        <v>PENDO</v>
+        <v>Busbar</v>
       </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="str">
+        <v>SLRDA</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K7">
         <v>2</v>
       </c>
-      <c r="I7" t="str">
+      <c r="L7" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7" t="str">
+      <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7">
+        <v>2</v>
+      </c>
+      <c r="O7" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M7" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N7">
+      <c r="P7" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q7">
+        <v>52</v>
+      </c>
+      <c r="R7">
         <v>48</v>
       </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7">
-        <v>12.8</v>
-      </c>
-      <c r="Q7" t="str">
+      <c r="S7">
+        <v>12.5</v>
+      </c>
+      <c r="T7" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R7" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S7" t="str">
-        <v/>
-      </c>
-      <c r="T7" t="str">
-        <v/>
-      </c>
       <c r="U7" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V7" t="str">
+        <v/>
+      </c>
+      <c r="W7" t="str">
+        <v/>
+      </c>
+      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
         <v/>
       </c>
     </row>
@@ -895,67 +958,76 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>SUTT 150 kV Tie Line SLRDA - PENDO</v>
+        <v>Salira Indah - Pendo</v>
       </c>
       <c r="D8" t="str">
         <v>PHT</v>
       </c>
       <c r="E8" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F8" t="str">
         <v>SLRDA</v>
       </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
       <c r="G8" t="str">
-        <v>PENDO</v>
+        <v>Busbar</v>
       </c>
       <c r="H8">
         <v>2</v>
       </c>
       <c r="I8" t="str">
+        <v>PENDO</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K8">
+        <v>2</v>
+      </c>
+      <c r="L8" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8" t="str">
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M8" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N8">
-        <v>32</v>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8">
-        <v>6.4</v>
-      </c>
-      <c r="Q8" t="str">
+      <c r="P8" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q8">
+        <v>45</v>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8">
+        <v>8.4</v>
+      </c>
+      <c r="T8" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R8" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S8" t="str">
-        <v>Interkoneksi antar bay busbar SLRDA dan PENDO.</v>
-      </c>
-      <c r="T8" t="str">
-        <v/>
-      </c>
       <c r="U8" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V8" t="str">
         <v/>
       </c>
-    </row>
-    <row r="9" xml:space="preserve">
+      <c r="W8" t="str">
+        <v/>
+      </c>
+      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -963,70 +1035,76 @@
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>SUTT 150 kV SRLYA - PENI (Ruas Suralaya - Peni)</v>
+        <v>Suralaya - Chandra Asri (PENI)</v>
       </c>
       <c r="D9" t="str">
         <v>PHT</v>
       </c>
       <c r="E9" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F9" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
       <c r="G9" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="str">
         <v>PENI</v>
       </c>
-      <c r="H9">
+      <c r="J9" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K9">
         <v>2</v>
       </c>
-      <c r="I9" t="str">
+      <c r="L9" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9" t="str">
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M9" t="str">
+      <c r="P9" t="str">
         <v>N-1</v>
       </c>
-      <c r="N9">
-        <v>74</v>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9">
-        <v>18.5</v>
-      </c>
-      <c r="Q9" t="str">
+      <c r="Q9">
+        <v>78</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9">
+        <v>15.2</v>
+      </c>
+      <c r="T9" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R9" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S9" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
-      </c>
-      <c r="T9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
-2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
-      </c>
-      <c r="U9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
-2. Pengaturan konfigurasi jaringan saat pemeliharaan.</v>
-      </c>
-      <c r="V9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Menengah :
-Usulan Double phi pada ruas Suralaya s.d Cilegon Lama. Diusulkan COD Tahun 2030.</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+      <c r="U9" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V9" t="str">
+        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Penyesuaian jadwal pemeliharaan.</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Double phi COD 2030.</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1034,65 +1112,73 @@
         <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v>SUTT 150 kV SRLYA - MCCI5 (Ruas Suralaya - MCCI)</v>
+        <v>Suralaya - MCCI</v>
       </c>
       <c r="D10" t="str">
         <v>PHT</v>
       </c>
       <c r="E10" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F10" t="str">
         <v>SRLYA</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
       <c r="G10" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
         <v>MCCI5</v>
       </c>
-      <c r="H10">
+      <c r="J10" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K10">
         <v>2</v>
       </c>
-      <c r="I10" t="str">
+      <c r="L10" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10" t="str">
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M10" t="str">
+      <c r="P10" t="str">
         <v>N-1</v>
       </c>
-      <c r="N10">
-        <v>71</v>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10">
-        <v>16.3</v>
-      </c>
-      <c r="Q10" t="str">
+      <c r="Q10">
+        <v>72</v>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10">
+        <v>16.8</v>
+      </c>
+      <c r="T10" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R10" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S10" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon masih single phi.</v>
-      </c>
-      <c r="T10" t="str">
-        <v>Pemadaman apabila terjadi gangguan N-1-1.</v>
-      </c>
       <c r="U10" t="str">
-        <v>Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.</v>
-      </c>
-      <c r="V10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Menengah :
-Usulan Double phi.</v>
+        <v>JBB</v>
+      </c>
+      <c r="V10" t="str">
+        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Pemadaman apabila terjadi trip.</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
       </c>
     </row>
     <row r="11">
@@ -1103,63 +1189,72 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>SUTT 150 kV CLBRU - CLGON Sirkit 1 (2 Line)</v>
+        <v>Cilegon Baru - Cilegon Lama (Sirkit 1)</v>
       </c>
       <c r="D11" t="str">
         <v>PHT</v>
       </c>
       <c r="E11" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F11" t="str">
         <v>CLBRU</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
       <c r="G11" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="str">
         <v>CLGON</v>
       </c>
-      <c r="H11">
+      <c r="J11" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K11">
         <v>2</v>
       </c>
-      <c r="I11" t="str">
+      <c r="L11" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>2</v>
       </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11" t="str">
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M11" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N11">
-        <v>62</v>
-      </c>
-      <c r="O11">
+      <c r="P11" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q11">
+        <v>54</v>
+      </c>
+      <c r="R11">
         <v>50</v>
       </c>
-      <c r="P11">
-        <v>11.2</v>
-      </c>
-      <c r="Q11" t="str">
+      <c r="S11">
+        <v>9.2</v>
+      </c>
+      <c r="T11" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R11" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S11" t="str">
-        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 1.</v>
-      </c>
-      <c r="T11" t="str">
-        <v/>
-      </c>
       <c r="U11" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V11" t="str">
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
         <v/>
       </c>
     </row>
@@ -1171,63 +1266,72 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>SUTT 150 kV CLBRU - CLGON Sirkit 2 (2 Line)</v>
+        <v>Cilegon Baru - Cilegon Lama (Sirkit 2)</v>
       </c>
       <c r="D12" t="str">
         <v>PHT</v>
       </c>
       <c r="E12" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F12" t="str">
         <v>CLBRU</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
       <c r="G12" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
         <v>CLGON</v>
       </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-      <c r="I12" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="J12">
-        <v>2</v>
+      <c r="J12" t="str">
+        <v>Busbar</v>
       </c>
       <c r="K12">
         <v>2</v>
       </c>
       <c r="L12" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12">
+        <v>2</v>
+      </c>
+      <c r="O12" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M12" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N12">
+      <c r="P12" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q12">
+        <v>54</v>
+      </c>
+      <c r="R12">
         <v>50</v>
       </c>
-      <c r="O12">
-        <v>62</v>
-      </c>
-      <c r="P12">
-        <v>11.2</v>
-      </c>
-      <c r="Q12" t="str">
+      <c r="S12">
+        <v>9.2</v>
+      </c>
+      <c r="T12" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R12" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S12" t="str">
-        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 2.</v>
-      </c>
-      <c r="T12" t="str">
-        <v/>
-      </c>
       <c r="U12" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V12" t="str">
+        <v/>
+      </c>
+      <c r="W12" t="str">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
         <v/>
       </c>
     </row>
@@ -1239,64 +1343,73 @@
         <v>3</v>
       </c>
       <c r="C13" t="str">
-        <v>SUTT 150 kV PENI - MTSUI (Ruas Peni - Mitsui)</v>
+        <v>Chandra Asri (PENI) - Mitsui (MTSUI)</v>
       </c>
       <c r="D13" t="str">
         <v>PHT</v>
       </c>
       <c r="E13" t="str">
+        <v>PHT</v>
+      </c>
+      <c r="F13" t="str">
         <v>PENI</v>
       </c>
-      <c r="F13">
+      <c r="G13" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="G13" t="str">
+      <c r="I13" t="str">
         <v>MTSUI</v>
       </c>
-      <c r="H13">
+      <c r="J13" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K13">
         <v>3</v>
       </c>
-      <c r="I13" t="str">
+      <c r="L13" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13" t="str">
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M13" t="str">
+      <c r="P13" t="str">
         <v>N-1</v>
       </c>
-      <c r="N13">
-        <v>68</v>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13">
-        <v>8.7</v>
-      </c>
-      <c r="Q13" t="str">
+      <c r="Q13">
+        <v>65</v>
+      </c>
+      <c r="R13" t="str">
+        <v/>
+      </c>
+      <c r="S13">
+        <v>6.8</v>
+      </c>
+      <c r="T13" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R13" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S13" t="str">
-        <v>Ruas Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
-      </c>
-      <c r="T13" t="str">
-        <v>Pemadaman apabila trip saat beban puncak.</v>
-      </c>
       <c r="U13" t="str">
-        <v>Pengaturan operasi terkoordinasi UP2B Banten.</v>
+        <v>JBB</v>
       </c>
       <c r="V13" t="str">
-        <v>Usulan Double phi.</v>
+        <v>Ruas Peni-Mitsui-Cilegon masih single phi.</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Pemadaman apabila trip.</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Jadwal pemeliharaan KTT.</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>Usulan double phi COD 2030.</v>
       </c>
     </row>
     <row r="14">
@@ -1304,67 +1417,76 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="C14" t="str">
-        <v>SUTT 150 kV MCCI5 - CLGON (Ruas MCCI - Cilegon)</v>
+        <v>Mitsui (MTSUI) - Cilegon Lama</v>
       </c>
       <c r="D14" t="str">
         <v>PHT</v>
       </c>
       <c r="E14" t="str">
-        <v>MCCI5</v>
-      </c>
-      <c r="F14">
+        <v>PHT</v>
+      </c>
+      <c r="F14" t="str">
+        <v>MTSUI</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K14">
         <v>2</v>
       </c>
-      <c r="G14" t="str">
-        <v>CLGON</v>
-      </c>
-      <c r="H14">
-        <v>2</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="L14" t="str">
         <v>150 kV</v>
       </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14" t="str">
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M14" t="str">
-        <v>N-1</v>
-      </c>
-      <c r="N14">
-        <v>65</v>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14">
-        <v>9.4</v>
-      </c>
-      <c r="Q14" t="str">
+      <c r="P14" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q14">
+        <v>48</v>
+      </c>
+      <c r="R14" t="str">
+        <v/>
+      </c>
+      <c r="S14">
+        <v>5.4</v>
+      </c>
+      <c r="T14" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R14" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S14" t="str">
-        <v>Ruas Suralaya–MCCI–Cilegon masih single phi.</v>
-      </c>
-      <c r="T14" t="str">
-        <v>Risiko keandalan suplai pelanggan industri.</v>
-      </c>
       <c r="U14" t="str">
-        <v>Penyesuaian pola operasi jaringan.</v>
+        <v>JBB</v>
       </c>
       <c r="V14" t="str">
-        <v>Usulan Double phi.</v>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <v/>
+      </c>
+      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1375,63 +1497,72 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Feeder Trafo SLRDA ke KTT SLFDO-1</v>
+        <v>Feeder Beban KTT SLFDO-1 (78 MVA)</v>
       </c>
       <c r="D15" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E15" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F15" t="str">
         <v>SLRDA</v>
       </c>
-      <c r="F15">
+      <c r="G15" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H15">
         <v>2</v>
       </c>
-      <c r="G15" t="str">
+      <c r="I15" t="str">
         <v>KTT SLFDO-1</v>
       </c>
-      <c r="H15">
+      <c r="J15" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K15">
         <v>3</v>
       </c>
-      <c r="I15" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
       <c r="L15" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M15" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N15">
-        <v>72</v>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15">
+      <c r="P15" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q15">
+        <v>78</v>
+      </c>
+      <c r="R15" t="str">
+        <v/>
+      </c>
+      <c r="S15">
         <v>1.2</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="T15" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R15" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S15" t="str">
-        <v>Suplai konsumen KTT SLFDO-1 Kapasitas 78 MVA.</v>
-      </c>
-      <c r="T15" t="str">
-        <v/>
-      </c>
       <c r="U15" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V15" t="str">
+        <v>Feeder Konsumen Industri KTT SLFDO-1</v>
+      </c>
+      <c r="W15" t="str">
+        <v/>
+      </c>
+      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
         <v/>
       </c>
     </row>
@@ -1443,63 +1574,72 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Feeder Trafo SLRDA ke KTT SLFDO-2</v>
+        <v>Feeder Beban KTT SLFDO-2 (30 MVA)</v>
       </c>
       <c r="D16" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E16" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F16" t="str">
         <v>SLRDA</v>
       </c>
-      <c r="F16">
+      <c r="G16" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H16">
         <v>2</v>
       </c>
-      <c r="G16" t="str">
+      <c r="I16" t="str">
         <v>KTT SLFDO-2</v>
       </c>
-      <c r="H16">
+      <c r="J16" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K16">
         <v>3</v>
       </c>
-      <c r="I16" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
       <c r="L16" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M16" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N16">
-        <v>65</v>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="str">
+      <c r="P16" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q16">
+        <v>30</v>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16">
+        <v>1.2</v>
+      </c>
+      <c r="T16" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R16" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S16" t="str">
-        <v>Suplai konsumen KTT SLFDO-2 Kapasitas 30 MVA.</v>
-      </c>
-      <c r="T16" t="str">
-        <v/>
-      </c>
       <c r="U16" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V16" t="str">
+        <v>Feeder Konsumen Industri KTT SLFDO-2</v>
+      </c>
+      <c r="W16" t="str">
+        <v/>
+      </c>
+      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
         <v/>
       </c>
     </row>
@@ -1511,63 +1651,72 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Feeder Trafo PENDO ke KTT PENDO</v>
+        <v>Feeder Beban KTT PENDO (35 MVA)</v>
       </c>
       <c r="D17" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E17" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F17" t="str">
         <v>PENDO</v>
       </c>
-      <c r="F17">
+      <c r="G17" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H17">
         <v>2</v>
       </c>
-      <c r="G17" t="str">
+      <c r="I17" t="str">
         <v>KTT PENDO</v>
       </c>
-      <c r="H17">
+      <c r="J17" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K17">
         <v>3</v>
       </c>
-      <c r="I17" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
       <c r="L17" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M17" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N17">
-        <v>58</v>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17">
+      <c r="P17" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q17">
+        <v>35</v>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17">
         <v>0.8</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="T17" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R17" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S17" t="str">
-        <v>Suplai konsumen KTT PENDO Kapasitas 35 MVA.</v>
-      </c>
-      <c r="T17" t="str">
-        <v/>
-      </c>
       <c r="U17" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V17" t="str">
+        <v>Feeder Konsumen Industri KTT PENDO</v>
+      </c>
+      <c r="W17" t="str">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
         <v/>
       </c>
     </row>
@@ -1576,66 +1725,75 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="C18" t="str">
-        <v>Feeder Trafo PENI ke KTT PENI</v>
+        <v>Feeder Beban KTT PENI (40 MVA)</v>
       </c>
       <c r="D18" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E18" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F18" t="str">
         <v>PENI</v>
       </c>
-      <c r="F18">
+      <c r="G18" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H18">
         <v>2</v>
       </c>
-      <c r="G18" t="str">
+      <c r="I18" t="str">
         <v>KTT PENI</v>
       </c>
-      <c r="H18">
+      <c r="J18" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K18">
         <v>3</v>
       </c>
-      <c r="I18" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
       <c r="L18" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M18" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N18">
-        <v>60</v>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-      <c r="P18">
-        <v>1.1</v>
-      </c>
-      <c r="Q18" t="str">
+      <c r="P18" t="str">
+        <v>N-1</v>
+      </c>
+      <c r="Q18">
+        <v>40</v>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18">
+        <v>0.5</v>
+      </c>
+      <c r="T18" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R18" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S18" t="str">
-        <v>Suplai konsumen KTT PENI Kapasitas 40 MVA.</v>
-      </c>
-      <c r="T18" t="str">
-        <v/>
-      </c>
       <c r="U18" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V18" t="str">
+        <v>Feeder Konsumen Industri KTT PENI</v>
+      </c>
+      <c r="W18" t="str">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
         <v/>
       </c>
     </row>
@@ -1647,63 +1805,72 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Feeder Trafo PENI ke KTT LCI (2 Line)</v>
+        <v>Feeder Beban KTT LCI (115 MVA)</v>
       </c>
       <c r="D19" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E19" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F19" t="str">
         <v>PENI</v>
       </c>
-      <c r="F19">
+      <c r="G19" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H19">
         <v>2</v>
       </c>
-      <c r="G19" t="str">
+      <c r="I19" t="str">
         <v>KTT LCI</v>
       </c>
-      <c r="H19">
+      <c r="J19" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K19">
         <v>3</v>
       </c>
-      <c r="I19" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J19">
+      <c r="L19" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M19">
         <v>2</v>
       </c>
-      <c r="K19">
-        <v>1</v>
-      </c>
-      <c r="L19" t="str">
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M19" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N19">
-        <v>64</v>
-      </c>
-      <c r="O19">
-        <v>60</v>
-      </c>
-      <c r="P19">
+      <c r="P19" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q19">
+        <v>58</v>
+      </c>
+      <c r="R19">
+        <v>57</v>
+      </c>
+      <c r="S19">
         <v>1.5</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="T19" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R19" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S19" t="str">
-        <v>Suplai 2 sirkit konsumen KTT LCI Kapasitas 115 MVA.</v>
-      </c>
-      <c r="T19" t="str">
-        <v/>
-      </c>
       <c r="U19" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V19" t="str">
+        <v>Feeder Konsumen Industri KTT LCI</v>
+      </c>
+      <c r="W19" t="str">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
         <v/>
       </c>
     </row>
@@ -1715,63 +1882,72 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Feeder Trafo MCCI5 ke KTT MCCI</v>
+        <v>Feeder Beban KTT MCCI (40 MVA)</v>
       </c>
       <c r="D20" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E20" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F20" t="str">
         <v>MCCI5</v>
       </c>
-      <c r="F20">
+      <c r="G20" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H20">
         <v>2</v>
       </c>
-      <c r="G20" t="str">
+      <c r="I20" t="str">
         <v>KTT MCCI</v>
       </c>
-      <c r="H20">
+      <c r="J20" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K20">
         <v>3</v>
       </c>
-      <c r="I20" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
       <c r="L20" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M20" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N20">
-        <v>55</v>
-      </c>
-      <c r="O20" t="str">
-        <v/>
-      </c>
-      <c r="P20">
-        <v>0.9</v>
-      </c>
-      <c r="Q20" t="str">
+      <c r="P20" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q20">
+        <v>40</v>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20">
+        <v>0.6</v>
+      </c>
+      <c r="T20" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R20" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S20" t="str">
-        <v>Suplai konsumen KTT MCCI Kapasitas 40 MVA.</v>
-      </c>
-      <c r="T20" t="str">
-        <v/>
-      </c>
       <c r="U20" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V20" t="str">
+        <v>Feeder Konsumen Industri KTT MCCI</v>
+      </c>
+      <c r="W20" t="str">
+        <v/>
+      </c>
+      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
         <v/>
       </c>
     </row>
@@ -1783,273 +1959,78 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>Feeder Trafo MTSUI ke KTT MTSUI</v>
+        <v>Feeder Beban KTT MTSUI (31 MVA)</v>
       </c>
       <c r="D21" t="str">
         <v>Feeder Beban</v>
       </c>
       <c r="E21" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F21" t="str">
         <v>MTSUI</v>
       </c>
-      <c r="F21">
+      <c r="G21" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H21">
         <v>3</v>
       </c>
-      <c r="G21" t="str">
+      <c r="I21" t="str">
         <v>KTT MTSUI</v>
       </c>
-      <c r="H21">
+      <c r="J21" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="K21">
         <v>4</v>
       </c>
-      <c r="I21" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
       <c r="L21" t="str">
+        <v>20 kV</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="str">
         <v>Beroperasi</v>
       </c>
-      <c r="M21" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N21">
-        <v>50</v>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-      <c r="P21">
-        <v>0.7</v>
-      </c>
-      <c r="Q21" t="str">
+      <c r="P21" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q21">
+        <v>31</v>
+      </c>
+      <c r="R21" t="str">
+        <v/>
+      </c>
+      <c r="S21">
+        <v>0.4</v>
+      </c>
+      <c r="T21" t="str">
         <v>Banten - Cilegon</v>
       </c>
-      <c r="R21" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S21" t="str">
-        <v>Suplai konsumen KTT MTSUI Kapasitas 31 MVA.</v>
-      </c>
-      <c r="T21" t="str">
-        <v/>
-      </c>
       <c r="U21" t="str">
-        <v/>
+        <v>JBB</v>
       </c>
       <c r="V21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <v>Feeder CLBRU ke KSTEL (Rencana)</v>
-      </c>
-      <c r="D22" t="str">
-        <v>PHT</v>
-      </c>
-      <c r="E22" t="str">
-        <v>CLBRU</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="str">
-        <v>KSTEL</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-      <c r="L22" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="M22" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N22">
-        <v>50</v>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-      <c r="P22">
-        <v>3.5</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="R22" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S22" t="str">
-        <v>Bay Rencana Penghantar KSTEL (Dashed Line).</v>
-      </c>
-      <c r="T22" t="str">
-        <v/>
-      </c>
-      <c r="U22" t="str">
-        <v/>
-      </c>
-      <c r="V22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v>Feeder CLBRU ke POSCO (Rencana)</v>
-      </c>
-      <c r="D23" t="str">
-        <v>PHT</v>
-      </c>
-      <c r="E23" t="str">
-        <v>CLBRU</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="str">
-        <v>POSCO</v>
-      </c>
-      <c r="H23">
-        <v>3</v>
-      </c>
-      <c r="I23" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="M23" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N23">
-        <v>50</v>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-      <c r="P23">
-        <v>4.2</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="R23" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S23" t="str">
-        <v>Bay Rencana Penghantar POSCO (Dashed Line).</v>
-      </c>
-      <c r="T23" t="str">
-        <v/>
-      </c>
-      <c r="U23" t="str">
-        <v/>
-      </c>
-      <c r="V23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v>Feeder CLGON ke KSTEL (Rencana)</v>
-      </c>
-      <c r="D24" t="str">
-        <v>PHT</v>
-      </c>
-      <c r="E24" t="str">
-        <v>CLGON</v>
-      </c>
-      <c r="F24">
-        <v>2</v>
-      </c>
-      <c r="G24" t="str">
-        <v>KSTEL-CLGON</v>
-      </c>
-      <c r="H24">
-        <v>3</v>
-      </c>
-      <c r="I24" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="M24" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="N24">
-        <v>50</v>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-      <c r="P24">
-        <v>2.8</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="R24" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="S24" t="str">
-        <v>Bay Rencana Penghantar KSTEL dari CLGON (Dashed Line).</v>
-      </c>
-      <c r="T24" t="str">
-        <v/>
-      </c>
-      <c r="U24" t="str">
-        <v/>
-      </c>
-      <c r="V24" t="str">
+        <v>Feeder Konsumen Industri KTT Mitsui</v>
+      </c>
+      <c r="W21" t="str">
+        <v/>
+      </c>
+      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2152,7 +2133,7 @@
         <v>JBB</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>Busbar 500 kV Suralaya Baru</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -2205,7 +2186,7 @@
         <v>JBB</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>Busbar 500 kV Suralaya</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -2258,7 +2239,7 @@
         <v>JBB</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>Busbar 500 kV Cilegon Baru</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -2281,7 +2262,7 @@
         <v>Unit 3</v>
       </c>
       <c r="D5" t="str">
-        <v>Generator</v>
+        <v>Pembangkit</v>
       </c>
       <c r="E5" t="str">
         <v>Normal</v>
@@ -2311,7 +2292,7 @@
         <v>JBB</v>
       </c>
       <c r="N5" t="str">
-        <v>Bay Pembangkit: 1. Pembangkit, 2. Trafo Step-Up, 3. CB</v>
+        <v>Bay Pembangkit: 1. Pembangkit, 2. Trafo Generator, 3. CB</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -2417,16 +2398,16 @@
         <v>JBB</v>
       </c>
       <c r="N7" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama.</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA).</v>
       </c>
       <c r="O7" t="str">
-        <v>Kondisi N-1-1 berdampak overload pada IBT Suralaya.</v>
+        <v>Overload pada IBT Suralaya.</v>
       </c>
       <c r="P7" t="str">
         <v>Terpasang DS OLS IBT 1,2 Suralaya.</v>
       </c>
       <c r="Q7" t="str">
-        <v>Uprating IBT–1 &amp; 2 menjadi 500 MVA.</v>
+        <v>Uprating IBT–1 &amp; 2 dari 250 MVA menjadi 500 MVA.</v>
       </c>
     </row>
     <row r="8">
@@ -2470,16 +2451,16 @@
         <v>JBB</v>
       </c>
       <c r="N8" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama.</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #4 Cilegon 500 MVA).</v>
       </c>
       <c r="O8" t="str">
-        <v>Overload saat gangguan kontinjensi.</v>
+        <v>Ketidakseimbangan beban.</v>
       </c>
       <c r="P8" t="str">
-        <v>Optimalisasi transfer trip dan defense scheme.</v>
+        <v>Optimalisasi transfer trip antar GI.</v>
       </c>
       <c r="Q8" t="str">
-        <v>Uprating IBT Suralaya.</v>
+        <v>Uprating IBT–1 &amp; 2 Suralaya menjadi 500 MVA.</v>
       </c>
     </row>
     <row r="9">
@@ -2487,16 +2468,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Gardu Induk SRLYA (150 kV)</v>
+        <v>GI Suralaya 150 kV (Rel Busbar)</v>
       </c>
       <c r="C9" t="str">
         <v>SRLYA</v>
       </c>
       <c r="D9" t="str">
-        <v>Wide Busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E9" t="str">
-        <v>Wide (Panjang)</v>
+        <v>Panjang (Wide Busbar)</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -2523,7 +2504,7 @@
         <v>JBB</v>
       </c>
       <c r="N9" t="str">
-        <v>Busbar 150 kV Suralaya (Membentang panjang menghubungkan Unit 3, IBT 2, IBT 1 ke SLRDA, PENDO, PENI, MCCI5)</v>
+        <v>Busbar 150 kV Suralaya (Menghubungkan IBT 1, IBT 2, dan Saluran Distribusi)</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -2540,16 +2521,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Gardu Induk CLBRU (150 kV)</v>
+        <v>GI Cilegon Baru 150 kV (Rel Busbar)</v>
       </c>
       <c r="C10" t="str">
         <v>CLBRU</v>
       </c>
       <c r="D10" t="str">
-        <v>Wide Busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E10" t="str">
-        <v>Wide (Panjang)</v>
+        <v>Panjang (Wide Busbar)</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -2576,7 +2557,7 @@
         <v>JBB</v>
       </c>
       <c r="N10" t="str">
-        <v>Busbar 150 kV Cilegon Baru (Membentang menghubungkan IBT 4 ke CLGON, KSTEL, POSCO)</v>
+        <v>Busbar 150 kV Cilegon Baru</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -2593,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Gardu Induk SLRDA (150 kV)</v>
+        <v>GI Salira Indah</v>
       </c>
       <c r="C11" t="str">
         <v>SLRDA</v>
@@ -2629,7 +2610,7 @@
         <v>JBB</v>
       </c>
       <c r="N11" t="str">
-        <v>Busbar 150 kV Salira Indah</v>
+        <v>Gardu Induk Salira Indah</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -2646,7 +2627,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Gardu Induk PENDO (150 kV)</v>
+        <v>GI Pendo</v>
       </c>
       <c r="C12" t="str">
         <v>PENDO</v>
@@ -2682,7 +2663,7 @@
         <v>JBB</v>
       </c>
       <c r="N12" t="str">
-        <v>Busbar 150 kV Pendo</v>
+        <v>Gardu Induk Pendo</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -2699,7 +2680,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Gardu Induk PENI (150 kV)</v>
+        <v>GI Chandra Asri (PENI)</v>
       </c>
       <c r="C13" t="str">
         <v>PENI</v>
@@ -2735,16 +2716,16 @@
         <v>JBB</v>
       </c>
       <c r="N13" t="str">
-        <v>Ruas Penghantar Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
       </c>
       <c r="O13" t="str">
-        <v>Pemadaman apabila terjadi gangguan N-1-1.</v>
+        <v>Pemadaman apabila terdapat gangguan N-1-1.</v>
       </c>
       <c r="P13" t="str">
-        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
+        <v>Pemeliharaan mengikuti jadwal KTT.</v>
       </c>
       <c r="Q13" t="str">
-        <v>Usulan Double phi.</v>
+        <v>Double phi COD 2030.</v>
       </c>
     </row>
     <row r="14">
@@ -2752,7 +2733,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Gardu Induk MCCI5 (150 kV)</v>
+        <v>GI Mitsubishi Chemical (MCCI)</v>
       </c>
       <c r="C14" t="str">
         <v>MCCI5</v>
@@ -2788,16 +2769,16 @@
         <v>JBB</v>
       </c>
       <c r="N14" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon masih single phi.</v>
+        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
       </c>
       <c r="O14" t="str">
-        <v>Pemeliharaan penghantar sulit dilakukan.</v>
+        <v>Pemadaman apabila gangguan.</v>
       </c>
       <c r="P14" t="str">
-        <v>Pengaturan konfigurasi jaringan.</v>
+        <v>Penyesuaian jadwal pemeliharaan.</v>
       </c>
       <c r="Q14" t="str">
-        <v>Usulan Double phi.</v>
+        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
       </c>
     </row>
     <row r="15">
@@ -2805,7 +2786,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Gardu Induk CLGON (150 kV)</v>
+        <v>GI Cilegon Lama</v>
       </c>
       <c r="C15" t="str">
         <v>CLGON</v>
@@ -2841,7 +2822,7 @@
         <v>JBB</v>
       </c>
       <c r="N15" t="str">
-        <v>Busbar 150 kV Cilegon Lama (Menerima 2 Line dari CLBRU)</v>
+        <v>Gardu Induk Cilegon Lama</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2858,7 +2839,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Gardu Induk MTSUI (150 kV)</v>
+        <v>GI Mitsui (MTSUI)</v>
       </c>
       <c r="C16" t="str">
         <v>MTSUI</v>
@@ -2894,16 +2875,16 @@
         <v>JBB</v>
       </c>
       <c r="N16" t="str">
-        <v>Ruas Peni–Mitsui–Cilegon masih single phi.</v>
+        <v>Ruas Mitsui-Cilegon single phi</v>
       </c>
       <c r="O16" t="str">
-        <v>Pemadaman apabila trip saat pembebanan tinggi.</v>
+        <v/>
       </c>
       <c r="P16" t="str">
-        <v>Pengaturan konfigurasi jaringan.</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v>Usulan Double phi.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3094,10 +3075,10 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>Normal</v>
+        <v>N-1</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="L20" t="str">
         <v>Banten</v>
@@ -3106,7 +3087,7 @@
         <v>JBB</v>
       </c>
       <c r="N20" t="str">
-        <v>Konsumen Tegangan Tinggi PENI</v>
+        <v>Konsumen Tegangan Tinggi PENI Chandra Asri</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -3159,7 +3140,7 @@
         <v>JBB</v>
       </c>
       <c r="N21" t="str">
-        <v>Konsumen Tegangan Tinggi LCI (Dipasok 2 Sirkit)</v>
+        <v>Konsumen KTT LCI</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -3212,7 +3193,7 @@
         <v>JBB</v>
       </c>
       <c r="N22" t="str">
-        <v>Konsumen Tegangan Tinggi MCCI</v>
+        <v>Konsumen KTT MCCI</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -3265,7 +3246,7 @@
         <v>JBB</v>
       </c>
       <c r="N23" t="str">
-        <v>Konsumen Tegangan Tinggi MTSUI</v>
+        <v>Konsumen KTT Mitsui</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -3286,7 +3267,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3307,70 +3288,70 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Peralatan (5)</v>
+        <v>Peralatan (1)</v>
       </c>
       <c r="B2" t="str">
-        <v>Busbar</v>
+        <v>Generator / Pembangkit</v>
       </c>
       <c r="C2" t="str">
-        <v>Batang Rel Horizontal Tebal (Cyan/Biru)</v>
+        <v>Lingkaran Hijau dengan Gelombang Sinus AC (~)</v>
       </c>
       <c r="D2" t="str">
-        <v>Batang konduktor utama di Gardu Induk (GI / GITET) yang mengumpulkan dan membagikan daya listrik.</v>
+        <v>Titik hulu pembangkit listrik utama (PLTU, PLTA, PLTG, PLTGU).</v>
       </c>
       <c r="E2" t="str">
-        <v>Suralaya Baru (500 kV), GI SLRDA (150 kV)</v>
+        <v>PLTU Suralaya Unit 3 (600 MW)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Peralatan (5)</v>
+        <v>Peralatan (2)</v>
       </c>
       <c r="B3" t="str">
-        <v>Wide Busbar</v>
+        <v>Trafo Generator (GSUT)</v>
       </c>
       <c r="C3" t="str">
-        <v>Batang Rel Horizontal Panjang Membentang</v>
+        <v>2 Lingkaran Interlocking (Atas: Hijau sisi Gen, Bawah: Merah sisi GI)</v>
       </c>
       <c r="D3" t="str">
-        <v>Batang rel busbar panjang untuk GI hub yang terhubung ke 3 atau lebih GI/feeder agar jalur transmisi tidak semrawut.</v>
+        <v>Trafo penaik tegangan generator (Generator Step-Up) dari 15-20 kV ke tegangan tinggi GI (150/500 kV).</v>
       </c>
       <c r="E3" t="str">
-        <v>SRLYA (150 kV), CLBRU (150 kV)</v>
+        <v>Bay Pembangkit ke Busbar GI</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Peralatan (5)</v>
+        <v>Switching (3)</v>
       </c>
       <c r="B4" t="str">
-        <v>Generator</v>
+        <v>CB / PMT (Pemutus Tenaga)</v>
       </c>
       <c r="C4" t="str">
-        <v>Lingkaran Hijau dengan Gelombang AC (~) &amp; Terminal Bulatan</v>
+        <v>Balok / Persegi Panjang Solid Merah Tegak dengan garis terminal</v>
       </c>
       <c r="D4" t="str">
-        <v>Unit pembangkit tenaga listrik (PLTU, PLTA, PLTGU) lengkap dengan bay PMT dan trafo penaik tegangan.</v>
+        <v>Circuit Breaker pada bay pengirim dan penerima GI ke GI untuk memutus beban dan gangguan arus pendek.</v>
       </c>
       <c r="E4" t="str">
-        <v>PLTU Suralaya Unit 3 (600 MW)</v>
+        <v>Bay Line, Bay IBT, Bay Trafo, Bay Generator</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Peralatan (5)</v>
+        <v>Peralatan (4)</v>
       </c>
       <c r="B5" t="str">
-        <v>IBT</v>
+        <v>IBT (Interbus Transformer)</v>
       </c>
       <c r="C5" t="str">
-        <v>3 Lingkaran Interlocking (Biru, Merah, Kuning) + Badge Nomor</v>
+        <v>3 Lingkaran Bertumpuk (Atas Biru 500kV, Kiri Merah 150kV, Kanan Kuning 33kV)</v>
       </c>
       <c r="D5" t="str">
-        <v>Inter-bus Transformer tegangan ekstra tinggi (500/150 kV atau 275/150 kV) dengan 3 belitan (primer, sekunder, tersier).</v>
+        <v>Trafo interkoneksi sistem transmisi tegangan ekstra tinggi (500/150 kV atau 275/150 kV).</v>
       </c>
       <c r="E5" t="str">
-        <v>IBT 1 Suralaya (250 MVA), IBT 4 Cilegon Baru (500 MVA)</v>
+        <v>IBT 1 &amp; 2 Suralaya (250 MVA), IBT 4 Cilegon (500 MVA)</v>
       </c>
     </row>
     <row r="6">
@@ -3378,106 +3359,72 @@
         <v>Peralatan (5)</v>
       </c>
       <c r="B6" t="str">
-        <v>Trafo</v>
+        <v>Trafo Distribusi</v>
       </c>
       <c r="C6" t="str">
-        <v>2 Lingkaran Interlocking (Merah &amp; Hijau) + Terminal Bulatan</v>
+        <v>2 Lingkaran Interlocking (Atas: Merah 150kV, Bawah: Kuning 20kV / 70kV)</v>
       </c>
       <c r="D6" t="str">
-        <v>Trafo penurun tegangan (Step-down / Distribusi) 150/20 kV untuk menyuplai penyulang beban lokal.</v>
+        <v>Trafo step-down daya di Gardu Induk yang menurunkan tegangan dari 150 kV ke 70 kV atau 20 kV.</v>
       </c>
       <c r="E6" t="str">
-        <v>Trafo Distribusi 150/20 kV GI Salira Indah</v>
+        <v>Trafo 150/20 kV GI Distribusi / Feeder KTT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Peralatan (5)</v>
+        <v>Peralatan (6)</v>
       </c>
       <c r="B7" t="str">
-        <v>Beban</v>
+        <v>Busbar</v>
       </c>
       <c r="C7" t="str">
-        <v>Segitiga Terbalik (∇) dengan Terminal Bulatan di Atas</v>
+        <v>Batang Rel Horizontal Tebal (Cyan/Biru)</v>
       </c>
       <c r="D7" t="str">
-        <v>Konsumen Tegangan Tinggi (KTT industri), penyulang distribusi, atau titik beban pemakaian tenaga listrik.</v>
+        <v>Batang konduktor utama di Gardu Induk (GI / GITET) yang mengumpulkan dan membagikan daya listrik.</v>
       </c>
       <c r="E7" t="str">
-        <v>KTT SLFDO-1 (78 MVA), KTT LCI (115 MVA), KTT MCCI</v>
+        <v>Suralaya Baru (500 kV), GI SRLYA 150 kV, GI CLBRU 150 kV</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Peralatan (5)</v>
+        <v>Peralatan (7)</v>
       </c>
       <c r="B8" t="str">
-        <v>PHT</v>
+        <v>Beban</v>
       </c>
       <c r="C8" t="str">
-        <v>Garis Kapsul Transmisi dengan 2 Bulatan di Kedua Ujung</v>
+        <v>Segitiga Terbalik (∇) Kuning Emas dengan terminal bulatan di atas</v>
       </c>
       <c r="D8" t="str">
-        <v>Penghantar Transmisi Saluran Udara (SUTET 500 kV / SUTT 150 kV) atau Saluran Kabel Bawah Tanah (SKTT).</v>
+        <v>Simbol resmi beban listrik konsumen industri KTT (Konsumen Tegangan Tinggi) atau feeder beban.</v>
       </c>
       <c r="E8" t="str">
-        <v>SUTT 150 kV SRLYA - PENI, SUTET 500 kV Tambun - Cawang</v>
+        <v>KTT SLFDO-1 (78 MVA), KTT PENI (40 MVA), KTT LCI (115 MVA)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Switching (2)</v>
+        <v>Peralatan (8)</v>
       </c>
       <c r="B9" t="str">
-        <v>PMT (Circuit Breaker)</v>
+        <v>PHT (Penghantar)</v>
       </c>
       <c r="C9" t="str">
-        <v>Sakelar Kontak Terbuka dengan Tanda Silang (X)</v>
+        <v>Kapsul Saluran Transmisi dengan dua bulatan terminal di ujung</v>
       </c>
       <c r="D9" t="str">
-        <v>Pemutus Tenaga: peralatan sakelar yang mampu membuka dan menutup sirkit dalam kondisi normal maupun kondisi hubung singkat (gangguan).</v>
+        <v>Saluran udara/kabel transmisi tenaga listrik penghubung antar gardu induk.</v>
       </c>
       <c r="E9" t="str">
-        <v>PMT Bay Pembangkit, PMT Bay IBT, PMT Bay Penghantar</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Switching (2)</v>
-      </c>
-      <c r="B10" t="str">
-        <v>PMS (Disconnector)</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Sakelar Pemisah dengan Garis Huruf (T)</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Pemisah: peralatan sakelar mekanis untuk memisahkan bagian instalasi yang bertegangan dari yang tidak bertegangan saat kondisi tanpa beban untuk keselamatan kerja.</v>
-      </c>
-      <c r="E10" t="str">
-        <v>PMS Busbar, PMS Line, PMS Tanah</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Penghubung (1)</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Connection Node</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Lingkaran Bulat Koneksi / Junction Point</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Titik simpul percabangan saluran listrik atau tap-off feeder.</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Junction busbar tap, simpul interkoneksi</v>
+        <v>PHT Suralaya - Salira Indah, PHT Suralaya - PENI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3564,8 +3511,8 @@
 2. Kondisi N–1–1 (IBT Suralaya dan IBT Cilegon) berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Rencana penambahan target DS OLS SS Suralaya 1,2.
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025).
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025).
 3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit–3 beroperasi.</v>
       </c>
       <c r="H3" t="str" xml:space="preserve">

--- a/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
+++ b/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
@@ -400,7 +400,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y28"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="4" max="4" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="16.83203125" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="17" max="17" width="24.83203125" customWidth="1"/>
+    <col min="18" max="18" width="24.83203125" customWidth="1"/>
+    <col min="19" max="19" width="22.83203125" customWidth="1"/>
+    <col min="20" max="20" width="22.83203125" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" customWidth="1"/>
+    <col min="22" max="22" width="45.83203125" customWidth="1"/>
+    <col min="23" max="23" width="35.83203125" customWidth="1"/>
+    <col min="24" max="24" width="35.83203125" customWidth="1"/>
+    <col min="25" max="25" width="35.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -479,27 +506,27 @@
         <v>Usulan / Solusi</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>1&amp;2</v>
+        <v/>
       </c>
       <c r="C2" t="str">
-        <v>Bay IBT 2 Suralaya Baru (500/150 kV)</v>
+        <v>Bay Evakuasi PLTU Suralaya Unit 3</v>
       </c>
       <c r="D2" t="str">
-        <v>Bay IBT</v>
+        <v>Bay Generator &amp; GSUT</v>
       </c>
       <c r="E2" t="str">
-        <v>IBT</v>
+        <v>trafo_generator</v>
       </c>
       <c r="F2" t="str">
-        <v>Suralaya Baru</v>
+        <v>Unit 3</v>
       </c>
       <c r="G2" t="str">
-        <v>Busbar</v>
+        <v>generator</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -508,13 +535,13 @@
         <v>SRLYA</v>
       </c>
       <c r="J2" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="str">
-        <v>500/150 kV</v>
+        <v>500 kV</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -526,16 +553,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P2" t="str">
-        <v>Sangat Rawan</v>
+        <v>Normal</v>
       </c>
       <c r="Q2">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="R2" t="str">
         <v/>
       </c>
       <c r="S2">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="T2" t="str">
         <v>Banten - Cilegon</v>
@@ -544,101 +571,98 @@
         <v>JBB</v>
       </c>
       <c r="V2" t="str">
+        <v>Bay Pembangkit Unit 3: 1. Generator (Hijau), 2. Trafo GSUT (Hijau-Merah), 3. CB PMT (Balok Merah)</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>1&amp;2</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Bay IBT 2 Suralaya Baru (500/150 kV)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Bay Interbus Transformer</v>
+      </c>
+      <c r="E3" t="str">
+        <v>ibt</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Suralaya Baru</v>
+      </c>
+      <c r="G3" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3" t="str">
+        <v>SRLYA</v>
+      </c>
+      <c r="J3" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3" t="str">
+        <v>500/150 kV</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Beroperasi</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Sangat Rawan</v>
+      </c>
+      <c r="Q3">
+        <v>88</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3">
+        <v>0.5</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U3" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V3" t="str">
         <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
       </c>
-      <c r="W2" t="str" xml:space="preserve">
+      <c r="W3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
 2. Pertumbuhan beban menjadi terhambat.
 3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
       </c>
-      <c r="X2" t="str" xml:space="preserve">
+      <c r="X3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW.
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
 3. Pemeliharaan IBT saat beban rendah.</v>
-      </c>
-      <c r="Y2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025.</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1&amp;2</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Bay IBT 1 Suralaya (500/150 kV)</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Bay IBT</v>
-      </c>
-      <c r="E3" t="str">
-        <v>IBT</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Suralaya</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Busbar</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3" t="str">
-        <v>SRLYA</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Busbar</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="str">
-        <v>500/150 kV</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Sangat Rawan</v>
-      </c>
-      <c r="Q3">
-        <v>84</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3">
-        <v>0.5</v>
-      </c>
-      <c r="T3" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U3" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V3" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
-      </c>
-      <c r="W3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
-2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="X3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya.
-2. Pemeliharaan IBT saat beban rendah.</v>
       </c>
       <c r="Y3" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2026.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD Tahun 2025.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -646,31 +670,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>2</v>
+        <v>1&amp;2</v>
       </c>
       <c r="C4" t="str">
-        <v>Bay IBT 4 Cilegon Baru (500/150 kV)</v>
+        <v>Bay IBT 1 Suralaya (500/150 kV)</v>
       </c>
       <c r="D4" t="str">
-        <v>Bay IBT</v>
+        <v>Bay Interbus Transformer</v>
       </c>
       <c r="E4" t="str">
-        <v>IBT</v>
+        <v>ibt</v>
       </c>
       <c r="F4" t="str">
-        <v>Cilegon Baru</v>
+        <v>Suralaya</v>
       </c>
       <c r="G4" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>CLBRU</v>
+        <v>SRLYA</v>
       </c>
       <c r="J4" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -691,7 +715,7 @@
         <v>Sangat Rawan</v>
       </c>
       <c r="Q4">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -706,55 +730,57 @@
         <v>JBB</v>
       </c>
       <c r="V4" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama.</v>
-      </c>
-      <c r="W4" t="str">
-        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="X4" t="str">
-        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
+      </c>
+      <c r="W4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
+2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+      </c>
+      <c r="X4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
+2. Pemeliharaan IBT saat beban rendah dan Unit 3 beroperasi.</v>
       </c>
       <c r="Y4" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA.</v>
-      </c>
-    </row>
-    <row r="5">
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD Tahun 2026.</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v>Bay Evakuasi Unit 3 PLTU Suralaya</v>
+        <v>Bay IBT 4 Cilegon Baru (500/150 kV)</v>
       </c>
       <c r="D5" t="str">
-        <v>Bay Generator</v>
+        <v>Bay Interbus Transformer</v>
       </c>
       <c r="E5" t="str">
-        <v>Trafo Generator</v>
+        <v>ibt</v>
       </c>
       <c r="F5" t="str">
-        <v>Unit 3</v>
+        <v>Cilegon Baru</v>
       </c>
       <c r="G5" t="str">
-        <v>Pembangkit</v>
+        <v>busbar</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>SRLYA</v>
+        <v>CLBRU</v>
       </c>
       <c r="J5" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="str">
-        <v>500 kV</v>
+        <v>500/150 kV</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -766,16 +792,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P5" t="str">
-        <v>Normal</v>
+        <v>Sangat Rawan</v>
       </c>
       <c r="Q5">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="str">
         <v>Banten - Cilegon</v>
@@ -784,16 +810,17 @@
         <v>JBB</v>
       </c>
       <c r="V5" t="str">
-        <v>Evakuasi daya PLTU Suralaya Unit 3 (1. Pembangkit, 2. Trafo Step-Up, 3. CB).</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #4 Cilegon 500 MVA sedangkan IBT #1,2 Suralaya 250 MVA).</v>
       </c>
       <c r="W5" t="str">
-        <v/>
+        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
       <c r="X5" t="str">
-        <v/>
-      </c>
-      <c r="Y5" t="str">
-        <v/>
+        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
+      </c>
+      <c r="Y5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Pendek :
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2026.</v>
       </c>
     </row>
     <row r="6">
@@ -804,19 +831,19 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>Suralaya - Salira Indah (Sirkit 1)</v>
+        <v>SUTT 150 kV SRLYA - SLRDA</v>
       </c>
       <c r="D6" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E6" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F6" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G6" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -825,7 +852,7 @@
         <v>SLRDA</v>
       </c>
       <c r="J6" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -834,7 +861,7 @@
         <v>150 kV</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -846,13 +873,13 @@
         <v>Normal</v>
       </c>
       <c r="Q6">
-        <v>52</v>
-      </c>
-      <c r="R6">
-        <v>48</v>
+        <v>54</v>
+      </c>
+      <c r="R6" t="str">
+        <v/>
       </c>
       <c r="S6">
-        <v>12.5</v>
+        <v>14.2</v>
       </c>
       <c r="T6" t="str">
         <v>Banten - Cilegon</v>
@@ -881,28 +908,28 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>Suralaya - Salira Indah (Sirkit 2)</v>
+        <v>SUTT 150 kV SRLYA - PENDO</v>
       </c>
       <c r="D7" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E7" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F7" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G7" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>SLRDA</v>
+        <v>PENDO</v>
       </c>
       <c r="J7" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -911,10 +938,10 @@
         <v>150 kV</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="str">
         <v>Beroperasi</v>
@@ -923,13 +950,13 @@
         <v>Normal</v>
       </c>
       <c r="Q7">
-        <v>52</v>
-      </c>
-      <c r="R7">
         <v>48</v>
       </c>
+      <c r="R7" t="str">
+        <v/>
+      </c>
       <c r="S7">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="T7" t="str">
         <v>Banten - Cilegon</v>
@@ -958,19 +985,19 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>Salira Indah - Pendo</v>
+        <v>SUTT 150 kV Tie Line SLRDA - PENDO</v>
       </c>
       <c r="D8" t="str">
-        <v>PHT</v>
+        <v>Tie Line Interkoneksi</v>
       </c>
       <c r="E8" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F8" t="str">
         <v>SLRDA</v>
       </c>
       <c r="G8" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -979,7 +1006,7 @@
         <v>PENDO</v>
       </c>
       <c r="J8" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -1000,13 +1027,13 @@
         <v>Normal</v>
       </c>
       <c r="Q8">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="T8" t="str">
         <v>Banten - Cilegon</v>
@@ -1015,7 +1042,7 @@
         <v>JBB</v>
       </c>
       <c r="V8" t="str">
-        <v/>
+        <v>Interkoneksi antar bay busbar Salira Indah (SLRDA) dan Pendo (PENDO) di Tier 2.</v>
       </c>
       <c r="W8" t="str">
         <v/>
@@ -1027,7 +1054,7 @@
         <v/>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1035,19 +1062,19 @@
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>Suralaya - Chandra Asri (PENI)</v>
+        <v>SUTT 150 kV SRLYA - PENI</v>
       </c>
       <c r="D9" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E9" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F9" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G9" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1056,7 +1083,7 @@
         <v>PENI</v>
       </c>
       <c r="J9" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -1077,13 +1104,13 @@
         <v>N-1</v>
       </c>
       <c r="Q9">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9">
-        <v>15.2</v>
+        <v>18.5</v>
       </c>
       <c r="T9" t="str">
         <v>Banten - Cilegon</v>
@@ -1092,19 +1119,22 @@
         <v>JBB</v>
       </c>
       <c r="V9" t="str">
-        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
-      </c>
-      <c r="W9" t="str">
-        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
-      </c>
-      <c r="X9" t="str">
-        <v>Penyesuaian jadwal pemeliharaan.</v>
-      </c>
-      <c r="Y9" t="str">
-        <v>Double phi COD 2030.</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+      </c>
+      <c r="W9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
+2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
+      </c>
+      <c r="X9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
+2. Pengaturan konfigurasi jaringan saat pemeliharaan untuk mengurangi dampak padam.</v>
+      </c>
+      <c r="Y9" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Menengah :
+Usulan Double phi pada ruas Suralaya s.d Cilegon Lama (Kajian belum ada). Diusulkan COD Tahun 2030.</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1112,19 +1142,19 @@
         <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v>Suralaya - MCCI</v>
+        <v>SUTT 150 kV SRLYA - MCCI5</v>
       </c>
       <c r="D10" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E10" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F10" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G10" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1133,7 +1163,7 @@
         <v>MCCI5</v>
       </c>
       <c r="J10" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1154,13 +1184,13 @@
         <v>N-1</v>
       </c>
       <c r="Q10">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10">
-        <v>16.8</v>
+        <v>16.3</v>
       </c>
       <c r="T10" t="str">
         <v>Banten - Cilegon</v>
@@ -1169,57 +1199,60 @@
         <v>JBB</v>
       </c>
       <c r="V10" t="str">
-        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
-      </c>
-      <c r="W10" t="str">
-        <v>Pemadaman apabila terjadi trip.</v>
-      </c>
-      <c r="X10" t="str">
-        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
-      </c>
-      <c r="Y10" t="str">
-        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+      </c>
+      <c r="W10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
+2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
+      </c>
+      <c r="X10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
+2. Pengaturan konfigurasi jaringan saat pemeliharaan.</v>
+      </c>
+      <c r="Y10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Menengah :
+Usulan Double phi pada ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="C11" t="str">
-        <v>Cilegon Baru - Cilegon Lama (Sirkit 1)</v>
+        <v>SUTT 150 kV PENI - MTSUI</v>
       </c>
       <c r="D11" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E11" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F11" t="str">
-        <v>CLBRU</v>
+        <v>PENI</v>
       </c>
       <c r="G11" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="str">
-        <v>CLGON</v>
+        <v>MTSUI</v>
       </c>
       <c r="J11" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="str">
         <v>150 kV</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1228,16 +1261,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P11" t="str">
-        <v>Normal</v>
+        <v>N-1</v>
       </c>
       <c r="Q11">
-        <v>54</v>
-      </c>
-      <c r="R11">
-        <v>50</v>
+        <v>68</v>
+      </c>
+      <c r="R11" t="str">
+        <v/>
       </c>
       <c r="S11">
-        <v>9.2</v>
+        <v>8.7</v>
       </c>
       <c r="T11" t="str">
         <v>Banten - Cilegon</v>
@@ -1246,16 +1279,18 @@
         <v>JBB</v>
       </c>
       <c r="V11" t="str">
-        <v/>
-      </c>
-      <c r="W11" t="str">
-        <v/>
+        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+      </c>
+      <c r="W11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
+2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
       </c>
       <c r="X11" t="str">
-        <v/>
-      </c>
-      <c r="Y11" t="str">
-        <v/>
+        <v>1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.</v>
+      </c>
+      <c r="Y11" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Menengah :
+Usulan Double phi pada ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
       </c>
     </row>
     <row r="12">
@@ -1263,31 +1298,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="C12" t="str">
-        <v>Cilegon Baru - Cilegon Lama (Sirkit 2)</v>
+        <v>SUTT 150 kV MCCI5 - CLGON</v>
       </c>
       <c r="D12" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E12" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F12" t="str">
-        <v>CLBRU</v>
+        <v>MCCI5</v>
       </c>
       <c r="G12" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="str">
         <v>CLGON</v>
       </c>
       <c r="J12" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1296,25 +1331,25 @@
         <v>150 kV</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="str">
         <v>Beroperasi</v>
       </c>
       <c r="P12" t="str">
-        <v>Normal</v>
+        <v>N-1</v>
       </c>
       <c r="Q12">
-        <v>54</v>
-      </c>
-      <c r="R12">
-        <v>50</v>
+        <v>65</v>
+      </c>
+      <c r="R12" t="str">
+        <v/>
       </c>
       <c r="S12">
-        <v>9.2</v>
+        <v>9.4</v>
       </c>
       <c r="T12" t="str">
         <v>Banten - Cilegon</v>
@@ -1323,16 +1358,16 @@
         <v>JBB</v>
       </c>
       <c r="V12" t="str">
-        <v/>
+        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
       </c>
       <c r="W12" t="str">
-        <v/>
+        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
       </c>
       <c r="X12" t="str">
-        <v/>
+        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
       </c>
       <c r="Y12" t="str">
-        <v/>
+        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
       </c>
     </row>
     <row r="13">
@@ -1343,31 +1378,31 @@
         <v>3</v>
       </c>
       <c r="C13" t="str">
-        <v>Chandra Asri (PENI) - Mitsui (MTSUI)</v>
+        <v>SUTT 150 kV MTSUI - CLGON</v>
       </c>
       <c r="D13" t="str">
-        <v>PHT</v>
+        <v>Saluran Udara (SUTT)</v>
       </c>
       <c r="E13" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F13" t="str">
-        <v>PENI</v>
+        <v>MTSUI</v>
       </c>
       <c r="G13" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="J13" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="K13">
         <v>2</v>
-      </c>
-      <c r="I13" t="str">
-        <v>MTSUI</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Busbar</v>
-      </c>
-      <c r="K13">
-        <v>3</v>
       </c>
       <c r="L13" t="str">
         <v>150 kV</v>
@@ -1385,13 +1420,13 @@
         <v>N-1</v>
       </c>
       <c r="Q13">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="T13" t="str">
         <v>Banten - Cilegon</v>
@@ -1400,16 +1435,16 @@
         <v>JBB</v>
       </c>
       <c r="V13" t="str">
-        <v>Ruas Peni-Mitsui-Cilegon masih single phi.</v>
+        <v>Ruas Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
       </c>
       <c r="W13" t="str">
-        <v>Pemadaman apabila trip.</v>
+        <v>Pemadaman apabila terjadi gangguan N-1.</v>
       </c>
       <c r="X13" t="str">
-        <v>Jadwal pemeliharaan KTT.</v>
+        <v>Pengaturan konfigurasi jaringan sistem Banten.</v>
       </c>
       <c r="Y13" t="str">
-        <v>Usulan double phi COD 2030.</v>
+        <v>Double phi ruas Suralaya s.d Cilegon Lama.</v>
       </c>
     </row>
     <row r="14">
@@ -1420,28 +1455,28 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Mitsui (MTSUI) - Cilegon Lama</v>
+        <v>SUTT 150 kV CLBRU - CLGON Sirkit 1</v>
       </c>
       <c r="D14" t="str">
-        <v>PHT</v>
+        <v>Double Circuit Line 1</v>
       </c>
       <c r="E14" t="str">
-        <v>PHT</v>
+        <v>cb</v>
       </c>
       <c r="F14" t="str">
-        <v>MTSUI</v>
+        <v>CLBRU</v>
       </c>
       <c r="G14" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <v>CLGON</v>
       </c>
       <c r="J14" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -1450,7 +1485,7 @@
         <v>150 kV</v>
       </c>
       <c r="M14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1462,13 +1497,13 @@
         <v>Normal</v>
       </c>
       <c r="Q14">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14">
-        <v>5.4</v>
+        <v>11.2</v>
       </c>
       <c r="T14" t="str">
         <v>Banten - Cilegon</v>
@@ -1477,7 +1512,7 @@
         <v>JBB</v>
       </c>
       <c r="V14" t="str">
-        <v/>
+        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 1.</v>
       </c>
       <c r="W14" t="str">
         <v/>
@@ -1497,40 +1532,40 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Feeder Beban KTT SLFDO-1 (78 MVA)</v>
+        <v>SUTT 150 kV CLBRU - CLGON Sirkit 2</v>
       </c>
       <c r="D15" t="str">
-        <v>Feeder Beban</v>
+        <v>Double Circuit Line 2</v>
       </c>
       <c r="E15" t="str">
-        <v>Beban</v>
+        <v>cb</v>
       </c>
       <c r="F15" t="str">
-        <v>SLRDA</v>
+        <v>CLBRU</v>
       </c>
       <c r="G15" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="J15" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="K15">
         <v>2</v>
       </c>
-      <c r="I15" t="str">
-        <v>KTT SLFDO-1</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Beban</v>
-      </c>
-      <c r="K15">
-        <v>3</v>
-      </c>
       <c r="L15" t="str">
-        <v>20 kV</v>
+        <v>150 kV</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="str">
         <v>Beroperasi</v>
@@ -1539,13 +1574,13 @@
         <v>Normal</v>
       </c>
       <c r="Q15">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="T15" t="str">
         <v>Banten - Cilegon</v>
@@ -1554,7 +1589,7 @@
         <v>JBB</v>
       </c>
       <c r="V15" t="str">
-        <v>Feeder Konsumen Industri KTT SLFDO-1</v>
+        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 2.</v>
       </c>
       <c r="W15" t="str">
         <v/>
@@ -1574,34 +1609,34 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Feeder Beban KTT SLFDO-2 (30 MVA)</v>
+        <v>Bay Trafo Distribusi SRLYA</v>
       </c>
       <c r="D16" t="str">
-        <v>Feeder Beban</v>
+        <v>Bay Trafo</v>
       </c>
       <c r="E16" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F16" t="str">
-        <v>SLRDA</v>
+        <v>SRLYA</v>
       </c>
       <c r="G16" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Trafo Distribusi SRLYA</v>
+      </c>
+      <c r="J16" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K16">
         <v>2</v>
       </c>
-      <c r="I16" t="str">
-        <v>KTT SLFDO-2</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Beban</v>
-      </c>
-      <c r="K16">
-        <v>3</v>
-      </c>
       <c r="L16" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -1616,13 +1651,13 @@
         <v>Normal</v>
       </c>
       <c r="Q16">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="T16" t="str">
         <v>Banten - Cilegon</v>
@@ -1631,7 +1666,7 @@
         <v>JBB</v>
       </c>
       <c r="V16" t="str">
-        <v>Feeder Konsumen Industri KTT SLFDO-2</v>
+        <v>Trafo pemakaian sendiri / distribusi lokal 150/20 kV Suralaya.</v>
       </c>
       <c r="W16" t="str">
         <v/>
@@ -1651,34 +1686,34 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Feeder Beban KTT PENDO (35 MVA)</v>
+        <v>Bay Trafo Distribusi CLBRU</v>
       </c>
       <c r="D17" t="str">
-        <v>Feeder Beban</v>
+        <v>Bay Trafo</v>
       </c>
       <c r="E17" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F17" t="str">
-        <v>PENDO</v>
+        <v>CLBRU</v>
       </c>
       <c r="G17" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Trafo Distribusi CLBRU</v>
+      </c>
+      <c r="J17" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K17">
         <v>2</v>
       </c>
-      <c r="I17" t="str">
-        <v>KTT PENDO</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Beban</v>
-      </c>
-      <c r="K17">
-        <v>3</v>
-      </c>
       <c r="L17" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1693,13 +1728,13 @@
         <v>Normal</v>
       </c>
       <c r="Q17">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="T17" t="str">
         <v>Banten - Cilegon</v>
@@ -1708,7 +1743,7 @@
         <v>JBB</v>
       </c>
       <c r="V17" t="str">
-        <v>Feeder Konsumen Industri KTT PENDO</v>
+        <v>Trafo distribusi lokal 150/20 kV Cilegon Baru.</v>
       </c>
       <c r="W17" t="str">
         <v/>
@@ -1725,37 +1760,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>Feeder Beban KTT PENI (40 MVA)</v>
+        <v>Feeder Trafo SLRDA ke KTT SLFDO-1</v>
       </c>
       <c r="D18" t="str">
-        <v>Feeder Beban</v>
+        <v>Feeder KTT</v>
       </c>
       <c r="E18" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F18" t="str">
-        <v>PENI</v>
+        <v>SLRDA</v>
       </c>
       <c r="G18" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="str">
-        <v>KTT PENI</v>
+        <v>KTT SLFDO-1</v>
       </c>
       <c r="J18" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="K18">
         <v>3</v>
       </c>
       <c r="L18" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M18">
         <v>1</v>
@@ -1767,16 +1802,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P18" t="str">
-        <v>N-1</v>
+        <v>Normal</v>
       </c>
       <c r="Q18">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="T18" t="str">
         <v>Banten - Cilegon</v>
@@ -1785,7 +1820,7 @@
         <v>JBB</v>
       </c>
       <c r="V18" t="str">
-        <v>Feeder Konsumen Industri KTT PENI</v>
+        <v>Suplai konsumen KTT SLFDO-1 Kapasitas 78 MVA</v>
       </c>
       <c r="W18" t="str">
         <v/>
@@ -1805,37 +1840,37 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Feeder Beban KTT LCI (115 MVA)</v>
+        <v>Feeder Trafo SLRDA ke KTT SLFDO-2</v>
       </c>
       <c r="D19" t="str">
-        <v>Feeder Beban</v>
+        <v>Feeder KTT</v>
       </c>
       <c r="E19" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F19" t="str">
-        <v>PENI</v>
+        <v>SLRDA</v>
       </c>
       <c r="G19" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="str">
-        <v>KTT LCI</v>
+        <v>KTT SLFDO-2</v>
       </c>
       <c r="J19" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -1847,13 +1882,13 @@
         <v>Normal</v>
       </c>
       <c r="Q19">
-        <v>58</v>
-      </c>
-      <c r="R19">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="R19" t="str">
+        <v/>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="str">
         <v>Banten - Cilegon</v>
@@ -1862,7 +1897,7 @@
         <v>JBB</v>
       </c>
       <c r="V19" t="str">
-        <v>Feeder Konsumen Industri KTT LCI</v>
+        <v>Suplai konsumen KTT SLFDO-2 Kapasitas 30 MVA</v>
       </c>
       <c r="W19" t="str">
         <v/>
@@ -1882,34 +1917,34 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Feeder Beban KTT MCCI (40 MVA)</v>
+        <v>Feeder Trafo PENDO ke KTT PENDO</v>
       </c>
       <c r="D20" t="str">
-        <v>Feeder Beban</v>
+        <v>Feeder KTT</v>
       </c>
       <c r="E20" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F20" t="str">
-        <v>MCCI5</v>
+        <v>PENDO</v>
       </c>
       <c r="G20" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20" t="str">
-        <v>KTT MCCI</v>
+        <v>KTT PENDO</v>
       </c>
       <c r="J20" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -1924,13 +1959,13 @@
         <v>Normal</v>
       </c>
       <c r="Q20">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="T20" t="str">
         <v>Banten - Cilegon</v>
@@ -1939,7 +1974,7 @@
         <v>JBB</v>
       </c>
       <c r="V20" t="str">
-        <v>Feeder Konsumen Industri KTT MCCI</v>
+        <v>Suplai konsumen KTT PENDO Kapasitas 35 MVA</v>
       </c>
       <c r="W20" t="str">
         <v/>
@@ -1956,37 +1991,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="C21" t="str">
-        <v>Feeder Beban KTT MTSUI (31 MVA)</v>
+        <v>Feeder Trafo PENI ke KTT PENI</v>
       </c>
       <c r="D21" t="str">
-        <v>Feeder Beban</v>
+        <v>Feeder KTT</v>
       </c>
       <c r="E21" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="F21" t="str">
-        <v>MTSUI</v>
+        <v>PENI</v>
       </c>
       <c r="G21" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21" t="str">
+        <v>KTT PENI</v>
+      </c>
+      <c r="J21" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K21">
         <v>3</v>
       </c>
-      <c r="I21" t="str">
-        <v>KTT MTSUI</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Beban</v>
-      </c>
-      <c r="K21">
-        <v>4</v>
-      </c>
       <c r="L21" t="str">
-        <v>20 kV</v>
+        <v>150/20 kV</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -1998,16 +2033,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P21" t="str">
-        <v>Normal</v>
+        <v>N-1</v>
       </c>
       <c r="Q21">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="T21" t="str">
         <v>Banten - Cilegon</v>
@@ -2016,28 +2051,586 @@
         <v>JBB</v>
       </c>
       <c r="V21" t="str">
-        <v>Feeder Konsumen Industri KTT Mitsui</v>
+        <v>Suplai konsumen KTT PENI Chandra Asri Kapasitas 40 MVA</v>
       </c>
       <c r="W21" t="str">
-        <v/>
+        <v>Terdapat risiko suplai saat pemeliharaan ruas single phi.</v>
       </c>
       <c r="X21" t="str">
-        <v/>
+        <v>Penyesuaian jadwal dengan konsumen industri.</v>
       </c>
       <c r="Y21" t="str">
+        <v>Usulan double phi transmisi 150 kV.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v/>
+      </c>
+      <c r="C22" t="str">
+        <v>Feeder Trafo PENI ke KTT LCI</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Feeder KTT</v>
+      </c>
+      <c r="E22" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PENI</v>
+      </c>
+      <c r="G22" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22" t="str">
+        <v>KTT LCI</v>
+      </c>
+      <c r="J22" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="M22">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Beroperasi</v>
+      </c>
+      <c r="P22" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q22">
+        <v>64</v>
+      </c>
+      <c r="R22" t="str">
+        <v/>
+      </c>
+      <c r="S22">
+        <v>1.5</v>
+      </c>
+      <c r="T22" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U22" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V22" t="str">
+        <v>Suplai 2 sirkit konsumen KTT LCI Kapasitas 115 MVA</v>
+      </c>
+      <c r="W22" t="str">
+        <v/>
+      </c>
+      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v/>
+      </c>
+      <c r="C23" t="str">
+        <v>Feeder Trafo MCCI5 ke KTT MCCI</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Feeder KTT</v>
+      </c>
+      <c r="E23" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="F23" t="str">
+        <v>MCCI5</v>
+      </c>
+      <c r="G23" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23" t="str">
+        <v>KTT MCCI</v>
+      </c>
+      <c r="J23" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Beroperasi</v>
+      </c>
+      <c r="P23" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q23">
+        <v>55</v>
+      </c>
+      <c r="R23" t="str">
+        <v/>
+      </c>
+      <c r="S23">
+        <v>0.9</v>
+      </c>
+      <c r="T23" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U23" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V23" t="str">
+        <v>Suplai konsumen KTT MCCI Kapasitas 40 MVA</v>
+      </c>
+      <c r="W23" t="str">
+        <v/>
+      </c>
+      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v>Bay Trafo Distribusi CLGON</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Bay Trafo</v>
+      </c>
+      <c r="E24" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="F24" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="G24" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H24">
+        <v>2</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Trafo Distribusi CLGON</v>
+      </c>
+      <c r="J24" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K24">
+        <v>3</v>
+      </c>
+      <c r="L24" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="M24">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>1</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Beroperasi</v>
+      </c>
+      <c r="P24" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q24">
+        <v>52</v>
+      </c>
+      <c r="R24" t="str">
+        <v/>
+      </c>
+      <c r="S24">
+        <v>0.1</v>
+      </c>
+      <c r="T24" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U24" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V24" t="str">
+        <v>Trafo distribusi lokal 150/20 kV Cilegon Lama.</v>
+      </c>
+      <c r="W24" t="str">
+        <v/>
+      </c>
+      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v>Feeder Trafo MTSUI ke KTT MTSUI</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Feeder KTT</v>
+      </c>
+      <c r="E25" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="F25" t="str">
+        <v>MTSUI</v>
+      </c>
+      <c r="G25" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25" t="str">
+        <v>KTT MTSUI</v>
+      </c>
+      <c r="J25" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Beroperasi</v>
+      </c>
+      <c r="P25" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q25">
+        <v>50</v>
+      </c>
+      <c r="R25" t="str">
+        <v/>
+      </c>
+      <c r="S25">
+        <v>0.7</v>
+      </c>
+      <c r="T25" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U25" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V25" t="str">
+        <v>Suplai konsumen KTT MTSUI Kapasitas 31 MVA</v>
+      </c>
+      <c r="W25" t="str">
+        <v/>
+      </c>
+      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v/>
+      </c>
+      <c r="C26" t="str">
+        <v>Bay Feeder CLBRU ke KSTEL (Rencana)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Bay Rencana</v>
+      </c>
+      <c r="E26" t="str">
+        <v>cb</v>
+      </c>
+      <c r="F26" t="str">
+        <v>CLBRU</v>
+      </c>
+      <c r="G26" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26" t="str">
+        <v>KSTEL</v>
+      </c>
+      <c r="J26" t="str">
+        <v>cb</v>
+      </c>
+      <c r="K26">
+        <v>3</v>
+      </c>
+      <c r="L26" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Rencana</v>
+      </c>
+      <c r="P26" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26" t="str">
+        <v/>
+      </c>
+      <c r="S26">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U26" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V26" t="str">
+        <v>Bay Rencana Penghantar KSTEL (Dashed Line)</v>
+      </c>
+      <c r="W26" t="str">
+        <v/>
+      </c>
+      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v/>
+      </c>
+      <c r="C27" t="str">
+        <v>Bay Feeder CLBRU ke POSCO (Rencana)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Bay Rencana</v>
+      </c>
+      <c r="E27" t="str">
+        <v>cb</v>
+      </c>
+      <c r="F27" t="str">
+        <v>CLBRU</v>
+      </c>
+      <c r="G27" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27" t="str">
+        <v>POSCO</v>
+      </c>
+      <c r="J27" t="str">
+        <v>cb</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
+      </c>
+      <c r="L27" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Rencana</v>
+      </c>
+      <c r="P27" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="str">
+        <v/>
+      </c>
+      <c r="S27">
+        <v>4.2</v>
+      </c>
+      <c r="T27" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U27" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V27" t="str">
+        <v>Bay Rencana Penghantar POSCO (Dashed Line)</v>
+      </c>
+      <c r="W27" t="str">
+        <v/>
+      </c>
+      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v/>
+      </c>
+      <c r="C28" t="str">
+        <v>Bay Feeder CLGON ke KSTEL (Rencana)</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Bay Rencana</v>
+      </c>
+      <c r="E28" t="str">
+        <v>cb</v>
+      </c>
+      <c r="F28" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="G28" t="str">
+        <v>busbar</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" t="str">
+        <v>KSTEL</v>
+      </c>
+      <c r="J28" t="str">
+        <v>cb</v>
+      </c>
+      <c r="K28">
+        <v>3</v>
+      </c>
+      <c r="L28" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Rencana</v>
+      </c>
+      <c r="P28" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="str">
+        <v/>
+      </c>
+      <c r="S28">
+        <v>2.8</v>
+      </c>
+      <c r="T28" t="str">
+        <v>Banten - Cilegon</v>
+      </c>
+      <c r="U28" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="V28" t="str">
+        <v>Bay Rencana Penghantar KSTEL dari CLGON (Dashed Line)</v>
+      </c>
+      <c r="W28" t="str">
+        <v/>
+      </c>
+      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q28"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="16.83203125" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" customWidth="1"/>
+    <col min="14" max="14" width="45.83203125" customWidth="1"/>
+    <col min="15" max="15" width="35.83203125" customWidth="1"/>
+    <col min="16" max="16" width="35.83203125" customWidth="1"/>
+    <col min="17" max="17" width="35.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2103,10 +2696,10 @@
         <v>Suralaya Baru</v>
       </c>
       <c r="D2" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E2" t="str">
-        <v>Normal</v>
+        <v>Panjang (Wide Busbar)</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -2133,7 +2726,7 @@
         <v>JBB</v>
       </c>
       <c r="N2" t="str">
-        <v>Busbar 500 kV Suralaya Baru</v>
+        <v>Rel Busbar 500 kV Suralaya Baru (Warna Biru)</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -2156,10 +2749,10 @@
         <v>Suralaya</v>
       </c>
       <c r="D3" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E3" t="str">
-        <v>Normal</v>
+        <v>Panjang (Wide Busbar)</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -2186,7 +2779,7 @@
         <v>JBB</v>
       </c>
       <c r="N3" t="str">
-        <v>Busbar 500 kV Suralaya</v>
+        <v>Rel Busbar 500 kV Suralaya (Warna Biru)</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -2209,10 +2802,10 @@
         <v>Cilegon Baru</v>
       </c>
       <c r="D4" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E4" t="str">
-        <v>Normal</v>
+        <v>Panjang (Wide Busbar)</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -2239,7 +2832,7 @@
         <v>JBB</v>
       </c>
       <c r="N4" t="str">
-        <v>Busbar 500 kV Cilegon Baru</v>
+        <v>Rel Busbar 500 kV Cilegon Baru (Warna Biru)</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -2262,7 +2855,7 @@
         <v>Unit 3</v>
       </c>
       <c r="D5" t="str">
-        <v>Pembangkit</v>
+        <v>generator</v>
       </c>
       <c r="E5" t="str">
         <v>Normal</v>
@@ -2292,7 +2885,7 @@
         <v>JBB</v>
       </c>
       <c r="N5" t="str">
-        <v>Bay Pembangkit: 1. Pembangkit, 2. Trafo Generator, 3. CB</v>
+        <v>Generator Pembangkit Unit 3 (Lingkaran Hijau + Simbol AC ~) dengan Step-up GSUT</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -2304,7 +2897,7 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2315,7 +2908,7 @@
         <v>IBT 2 SRL-BARU</v>
       </c>
       <c r="D6" t="str">
-        <v>IBT</v>
+        <v>ibt</v>
       </c>
       <c r="E6" t="str">
         <v>Normal</v>
@@ -2345,19 +2938,24 @@
         <v>JBB</v>
       </c>
       <c r="N6" t="str">
-        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi.</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Pemadaman apabila trip salah satu IBT.</v>
-      </c>
-      <c r="P6" t="str">
-        <v>Terpasang DS OLS IBT 1,2 Suralaya.</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>Uprating IBT–1 &amp; 2 dari 250 MVA menjadi 500 MVA.</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
+      </c>
+      <c r="O6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
+2. Pertumbuhan beban menjadi terhambat.
+3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
+      </c>
+      <c r="P6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
+3. Pemeliharaan IBT saat beban rendah.</v>
+      </c>
+      <c r="Q6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Pendek :
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2025.</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2368,7 +2966,7 @@
         <v>IBT 1 SRLYA</v>
       </c>
       <c r="D7" t="str">
-        <v>IBT</v>
+        <v>ibt</v>
       </c>
       <c r="E7" t="str">
         <v>Normal</v>
@@ -2398,19 +2996,22 @@
         <v>JBB</v>
       </c>
       <c r="N7" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA).</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Overload pada IBT Suralaya.</v>
-      </c>
-      <c r="P7" t="str">
-        <v>Terpasang DS OLS IBT 1,2 Suralaya.</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>Uprating IBT–1 &amp; 2 dari 250 MVA menjadi 500 MVA.</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
+      </c>
+      <c r="O7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
+2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+      </c>
+      <c r="P7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya.
+2. Pemeliharaan IBT saat beban rendah.</v>
+      </c>
+      <c r="Q7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Pendek :
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2026.</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2421,7 +3022,7 @@
         <v>IBT 4 CLBRU</v>
       </c>
       <c r="D8" t="str">
-        <v>IBT</v>
+        <v>ibt</v>
       </c>
       <c r="E8" t="str">
         <v>Normal</v>
@@ -2454,13 +3055,14 @@
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #4 Cilegon 500 MVA).</v>
       </c>
       <c r="O8" t="str">
-        <v>Ketidakseimbangan beban.</v>
+        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
       <c r="P8" t="str">
-        <v>Optimalisasi transfer trip antar GI.</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>Uprating IBT–1 &amp; 2 Suralaya menjadi 500 MVA.</v>
+        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
+      </c>
+      <c r="Q8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Pendek :
+Uprating IBT–1 &amp; 2 Suralaya menjadi 500 MVA.</v>
       </c>
     </row>
     <row r="9">
@@ -2468,13 +3070,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>GI Suralaya 150 kV (Rel Busbar)</v>
+        <v>Gardu Induk SRLYA (150 kV)</v>
       </c>
       <c r="C9" t="str">
         <v>SRLYA</v>
       </c>
       <c r="D9" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E9" t="str">
         <v>Panjang (Wide Busbar)</v>
@@ -2504,7 +3106,7 @@
         <v>JBB</v>
       </c>
       <c r="N9" t="str">
-        <v>Busbar 150 kV Suralaya (Menghubungkan IBT 1, IBT 2, dan Saluran Distribusi)</v>
+        <v>Busbar Utama 150 kV Suralaya (Tier 1, Merah Panjang menampung Unit 3, IBT 1, IBT 2, dan 5 Saluran ke Bawah)</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -2521,13 +3123,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>GI Cilegon Baru 150 kV (Rel Busbar)</v>
+        <v>Gardu Induk CLBRU (150 kV)</v>
       </c>
       <c r="C10" t="str">
         <v>CLBRU</v>
       </c>
       <c r="D10" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E10" t="str">
         <v>Panjang (Wide Busbar)</v>
@@ -2557,7 +3159,7 @@
         <v>JBB</v>
       </c>
       <c r="N10" t="str">
-        <v>Busbar 150 kV Cilegon Baru</v>
+        <v>Busbar Utama 150 kV Cilegon Baru (Tier 1, Merah Panjang menghubungkan IBT 4 ke CLGON, Trafo Lokal, KSTEL, POSCO)</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -2574,13 +3176,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>GI Salira Indah</v>
+        <v>Gardu Induk SLRDA (150 kV)</v>
       </c>
       <c r="C11" t="str">
         <v>SLRDA</v>
       </c>
       <c r="D11" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E11" t="str">
         <v>Normal</v>
@@ -2610,7 +3212,7 @@
         <v>JBB</v>
       </c>
       <c r="N11" t="str">
-        <v>Gardu Induk Salira Indah</v>
+        <v>Gardu Induk Salira Indah (Tier 2, Menyuplai KTT SLFDO-1 &amp; SLFDO-2)</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -2627,13 +3229,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>GI Pendo</v>
+        <v>Gardu Induk PENDO (150 kV)</v>
       </c>
       <c r="C12" t="str">
         <v>PENDO</v>
       </c>
       <c r="D12" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E12" t="str">
         <v>Normal</v>
@@ -2663,7 +3265,7 @@
         <v>JBB</v>
       </c>
       <c r="N12" t="str">
-        <v>Gardu Induk Pendo</v>
+        <v>Gardu Induk Pendo (Tier 2, Menyuplai KTT PENDO 35 MVA)</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -2680,13 +3282,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>GI Chandra Asri (PENI)</v>
+        <v>Gardu Induk PENI (150 kV)</v>
       </c>
       <c r="C13" t="str">
         <v>PENI</v>
       </c>
       <c r="D13" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E13" t="str">
         <v>Normal</v>
@@ -2716,16 +3318,16 @@
         <v>JBB</v>
       </c>
       <c r="N13" t="str">
-        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
+        <v>Ruas Penghantar Suralaya–PENI–Mitsui–Cilegon masih single phi.</v>
       </c>
       <c r="O13" t="str">
-        <v>Pemadaman apabila terdapat gangguan N-1-1.</v>
+        <v>Pemadaman apabila terdapat gangguan N–1–1.</v>
       </c>
       <c r="P13" t="str">
-        <v>Pemeliharaan mengikuti jadwal KTT.</v>
+        <v>Pemeliharaan mengikuti jadwal KTT industri.</v>
       </c>
       <c r="Q13" t="str">
-        <v>Double phi COD 2030.</v>
+        <v>Double phi transmisi 150 kV COD 2030.</v>
       </c>
     </row>
     <row r="14">
@@ -2733,13 +3335,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>GI Mitsubishi Chemical (MCCI)</v>
+        <v>Gardu Induk MCCI5 (150 kV)</v>
       </c>
       <c r="C14" t="str">
         <v>MCCI5</v>
       </c>
       <c r="D14" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E14" t="str">
         <v>Normal</v>
@@ -2769,13 +3371,13 @@
         <v>JBB</v>
       </c>
       <c r="N14" t="str">
-        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
+        <v>Ruas Penghantar Suralaya–MCCI–Cilegon masih single phi.</v>
       </c>
       <c r="O14" t="str">
-        <v>Pemadaman apabila gangguan.</v>
+        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
       </c>
       <c r="P14" t="str">
-        <v>Penyesuaian jadwal pemeliharaan.</v>
+        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
       </c>
       <c r="Q14" t="str">
         <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
@@ -2786,13 +3388,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>GI Cilegon Lama</v>
+        <v>Gardu Induk CLGON (150 kV)</v>
       </c>
       <c r="C15" t="str">
         <v>CLGON</v>
       </c>
       <c r="D15" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E15" t="str">
         <v>Normal</v>
@@ -2822,7 +3424,7 @@
         <v>JBB</v>
       </c>
       <c r="N15" t="str">
-        <v>Gardu Induk Cilegon Lama</v>
+        <v>Gardu Induk Cilegon Lama (Menerima double circuit dari CLBRU, serta loop dari MCCI5 dan MTSUI)</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -2839,13 +3441,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>GI Mitsui (MTSUI)</v>
+        <v>Gardu Induk MTSUI (150 kV)</v>
       </c>
       <c r="C16" t="str">
         <v>MTSUI</v>
       </c>
       <c r="D16" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="E16" t="str">
         <v>Normal</v>
@@ -2875,16 +3477,16 @@
         <v>JBB</v>
       </c>
       <c r="N16" t="str">
-        <v>Ruas Mitsui-Cilegon single phi</v>
+        <v>Ruas Peni–Mitsui–Cilegon masih single phi (Tier 3).</v>
       </c>
       <c r="O16" t="str">
-        <v/>
+        <v>Terjadi pemadaman apabila trip N-1.</v>
       </c>
       <c r="P16" t="str">
-        <v/>
+        <v>Pengaturan konfigurasi jaringan.</v>
       </c>
       <c r="Q16" t="str">
-        <v/>
+        <v>Double phi ruas Suralaya s.d Cilegon Lama.</v>
       </c>
     </row>
     <row r="17">
@@ -2892,13 +3494,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Konsumen KTT SLFDO-1 (78 MVA)</v>
+        <v>KTT SLFDO-1</v>
       </c>
       <c r="C17" t="str">
         <v>KTT SLFDO-1</v>
       </c>
       <c r="D17" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E17" t="str">
         <v>Normal</v>
@@ -2928,7 +3530,7 @@
         <v>JBB</v>
       </c>
       <c r="N17" t="str">
-        <v>Konsumen Tegangan Tinggi SLFDO-1</v>
+        <v>Konsumen Tegangan Tinggi SLFDO-1 (78 MVA)</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -2945,13 +3547,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Konsumen KTT SLFDO-2 (30 MVA)</v>
+        <v>KTT SLFDO-2</v>
       </c>
       <c r="C18" t="str">
         <v>KTT SLFDO-2</v>
       </c>
       <c r="D18" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E18" t="str">
         <v>Normal</v>
@@ -2981,7 +3583,7 @@
         <v>JBB</v>
       </c>
       <c r="N18" t="str">
-        <v>Konsumen Tegangan Tinggi SLFDO-2</v>
+        <v>Konsumen Tegangan Tinggi SLFDO-2 (30 MVA)</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -2998,13 +3600,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Konsumen KTT PENDO (35 MVA)</v>
+        <v>KTT PENDO</v>
       </c>
       <c r="C19" t="str">
         <v>KTT PENDO</v>
       </c>
       <c r="D19" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E19" t="str">
         <v>Normal</v>
@@ -3034,7 +3636,7 @@
         <v>JBB</v>
       </c>
       <c r="N19" t="str">
-        <v>Konsumen Tegangan Tinggi PENDO</v>
+        <v>Konsumen Tegangan Tinggi PENDO (35 MVA)</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -3051,13 +3653,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Konsumen KTT PENI (40 MVA)</v>
+        <v>KTT PENI</v>
       </c>
       <c r="C20" t="str">
         <v>KTT PENI</v>
       </c>
       <c r="D20" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E20" t="str">
         <v>Normal</v>
@@ -3087,16 +3689,16 @@
         <v>JBB</v>
       </c>
       <c r="N20" t="str">
-        <v>Konsumen Tegangan Tinggi PENI Chandra Asri</v>
+        <v>Konsumen Tegangan Tinggi PENI Chandra Asri (40 MVA, Memiliki Kerawanan #3)</v>
       </c>
       <c r="O20" t="str">
-        <v/>
+        <v>Potensi kendala operasional saat gangguan ruas single phi.</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>Jadwal pemeliharaan selaras dengan turn-around pabrik.</v>
       </c>
       <c r="Q20" t="str">
-        <v/>
+        <v>Usulan perkuatan sistem suplai transmisi.</v>
       </c>
     </row>
     <row r="21">
@@ -3104,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Konsumen KTT LCI (115 MVA)</v>
+        <v>KTT LCI</v>
       </c>
       <c r="C21" t="str">
         <v>KTT LCI</v>
       </c>
       <c r="D21" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E21" t="str">
         <v>Normal</v>
@@ -3140,7 +3742,7 @@
         <v>JBB</v>
       </c>
       <c r="N21" t="str">
-        <v>Konsumen KTT LCI</v>
+        <v>Konsumen KTT LCI (115 MVA, Disuplai 2 Sirkit dengan 2 PMT CB)</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -3157,13 +3759,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Konsumen KTT MCCI (40 MVA)</v>
+        <v>KTT MCCI</v>
       </c>
       <c r="C22" t="str">
         <v>KTT MCCI</v>
       </c>
       <c r="D22" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E22" t="str">
         <v>Normal</v>
@@ -3193,7 +3795,7 @@
         <v>JBB</v>
       </c>
       <c r="N22" t="str">
-        <v>Konsumen KTT MCCI</v>
+        <v>Konsumen Tegangan Tinggi MCCI (40 MVA)</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -3210,13 +3812,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Konsumen KTT MTSUI (31 MVA)</v>
+        <v>KTT MTSUI</v>
       </c>
       <c r="C23" t="str">
         <v>KTT MTSUI</v>
       </c>
       <c r="D23" t="str">
-        <v>Beban</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="E23" t="str">
         <v>Normal</v>
@@ -3246,7 +3848,7 @@
         <v>JBB</v>
       </c>
       <c r="N23" t="str">
-        <v>Konsumen KTT Mitsui</v>
+        <v>Konsumen Tegangan Tinggi Mitsui (31 MVA, Terhubung ke GI MTSUI)</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -3255,19 +3857,291 @@
         <v/>
       </c>
       <c r="Q23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Trafo Distribusi SRLYA</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Trafo SRLYA</v>
+      </c>
+      <c r="D24" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F24" t="str">
+        <v>60 MVA</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+      <c r="H24" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>Banten</v>
+      </c>
+      <c r="M24" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Trafo distribusi lokal 150/20 kV Suralaya</v>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Trafo Distribusi CLBRU</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Trafo CLBRU</v>
+      </c>
+      <c r="D25" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F25" t="str">
+        <v>60 MVA</v>
+      </c>
+      <c r="G25">
+        <v>2</v>
+      </c>
+      <c r="H25" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>Banten</v>
+      </c>
+      <c r="M25" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="N25" t="str">
+        <v>Trafo distribusi lokal 150/20 kV Cilegon Baru</v>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Trafo Distribusi CLGON</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Trafo CLGON</v>
+      </c>
+      <c r="D26" t="str">
+        <v>trafo_distribusi</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F26" t="str">
+        <v>60 MVA</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26" t="str">
+        <v>150/20 kV</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>Banten</v>
+      </c>
+      <c r="M26" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Trafo distribusi lokal 150/20 kV Cilegon Lama</v>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>KSTEL</v>
+      </c>
+      <c r="C27" t="str">
+        <v>KSTEL</v>
+      </c>
+      <c r="D27" t="str">
+        <v>cb</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>Banten</v>
+      </c>
+      <c r="M27" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Bay Rencana Konsumen Krakatau Steel (KSTEL) Garis Putus-putus</v>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>POSCO</v>
+      </c>
+      <c r="C28" t="str">
+        <v>POSCO</v>
+      </c>
+      <c r="D28" t="str">
+        <v>cb</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28" t="str">
+        <v>150 kV</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>Normal</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>Banten</v>
+      </c>
+      <c r="M28" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Bay Rencana Konsumen Krakatau Posco (POSCO) Garis Putus-putus</v>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q23"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q28"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E7"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" customWidth="1"/>
+    <col min="4" max="4" width="55.83203125" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3288,150 +4162,127 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Peralatan (1)</v>
+        <v>1. Pembangkit / Generator</v>
       </c>
       <c r="B2" t="str">
-        <v>Generator / Pembangkit</v>
+        <v>generator</v>
       </c>
       <c r="C2" t="str">
-        <v>Lingkaran Hijau dengan Gelombang Sinus AC (~)</v>
+        <v>Lingkaran Hijau + Simbol Gelombang AC (~)</v>
       </c>
       <c r="D2" t="str">
-        <v>Titik hulu pembangkit listrik utama (PLTU, PLTA, PLTG, PLTGU).</v>
+        <v>Digunakan untuk merepresentasikan sumber daya pembangkitan (PLTU, PLTGU, PLTA, dll). Pada diagram terletak di bagian paling atas (Unit 3).</v>
       </c>
       <c r="E2" t="str">
-        <v>PLTU Suralaya Unit 3 (600 MW)</v>
+        <v>PLTU Suralaya Unit 3, PLTGU Muara Karang Unit 1-3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Peralatan (2)</v>
+        <v>2. Trafo Generator (GSUT)</v>
       </c>
       <c r="B3" t="str">
-        <v>Trafo Generator (GSUT)</v>
+        <v>trafo_generator</v>
       </c>
       <c r="C3" t="str">
-        <v>2 Lingkaran Interlocking (Atas: Hijau sisi Gen, Bawah: Merah sisi GI)</v>
+        <v>Dua Cincin Bertaut: Atas Hijau (Generator), Bawah Merah (Tegangan Tinggi)</v>
       </c>
       <c r="D3" t="str">
-        <v>Trafo penaik tegangan generator (Generator Step-Up) dari 15-20 kV ke tegangan tinggi GI (150/500 kV).</v>
+        <v>Digunakan untuk menaikkan tegangan dari generator pembangkit ke tegangan sistem transmisi (Generator Step-Up Transformer / GSUT).</v>
       </c>
       <c r="E3" t="str">
-        <v>Bay Pembangkit ke Busbar GI</v>
+        <v>Trafo Step-Up PLTU Unit 3 ke Busbar 150 kV SRLYA</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Switching (3)</v>
+        <v>3. Circuit Breaker (PMT)</v>
       </c>
       <c r="B4" t="str">
-        <v>CB / PMT (Pemutus Tenaga)</v>
+        <v>cb</v>
       </c>
       <c r="C4" t="str">
-        <v>Balok / Persegi Panjang Solid Merah Tegak dengan garis terminal</v>
+        <v>Balok Persegi Merah Solid pada Jalur Penghantar</v>
       </c>
       <c r="D4" t="str">
-        <v>Circuit Breaker pada bay pengirim dan penerima GI ke GI untuk memutus beban dan gangguan arus pendek.</v>
+        <v>Pemutus Tenaga (PMT / Circuit Breaker) yang diletakkan pada bay pengirim maupun penerima GI ke GI untuk memutus arus gangguan.</v>
       </c>
       <c r="E4" t="str">
-        <v>Bay Line, Bay IBT, Bay Trafo, Bay Generator</v>
+        <v>Semua bay outgoing/incoming SUTT 150 kV, bay trafo, dan bay IBT</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Peralatan (4)</v>
+        <v>4. Interbus Transformer (IBT)</v>
       </c>
       <c r="B5" t="str">
-        <v>IBT (Interbus Transformer)</v>
+        <v>ibt</v>
       </c>
       <c r="C5" t="str">
-        <v>3 Lingkaran Bertumpuk (Atas Biru 500kV, Kiri Merah 150kV, Kanan Kuning 33kV)</v>
+        <v>Tiga Cincin Bertaut: Atas Biru (500 kV), Kiri Merah (150 kV), Kanan Kuning (Tertiary 33/20 kV)</v>
       </c>
       <c r="D5" t="str">
-        <v>Trafo interkoneksi sistem transmisi tegangan ekstra tinggi (500/150 kV atau 275/150 kV).</v>
+        <v>Transformator Daya Besar (3 Winding) penghubung antar grid tegangan ekstra tinggi 500 kV atau 275 kV ke tegangan transmisi 150 kV.</v>
       </c>
       <c r="E5" t="str">
-        <v>IBT 1 &amp; 2 Suralaya (250 MVA), IBT 4 Cilegon (500 MVA)</v>
+        <v>IBT 1 Suralaya (500/150 kV), IBT 2 Suralaya Baru, IBT 4 Cilegon Baru</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Peralatan (5)</v>
+        <v>5. Trafo Distribusi / KTT</v>
       </c>
       <c r="B6" t="str">
-        <v>Trafo Distribusi</v>
+        <v>trafo_distribusi</v>
       </c>
       <c r="C6" t="str">
-        <v>2 Lingkaran Interlocking (Atas: Merah 150kV, Bawah: Kuning 20kV / 70kV)</v>
+        <v>Dua Cincin Bertaut: Atas Merah (150 kV), Bawah Kuning (20 kV / 70 kV)</v>
       </c>
       <c r="D6" t="str">
-        <v>Trafo step-down daya di Gardu Induk yang menurunkan tegangan dari 150 kV ke 70 kV atau 20 kV.</v>
+        <v>Transformator penurun tegangan dari transmisi 150 kV ke tegangan menengah 20 kV (atau 70 kV) untuk melayani gardu distribusi &amp; konsumen tegangan tinggi (KTT).</v>
       </c>
       <c r="E6" t="str">
-        <v>Trafo 150/20 kV GI Distribusi / Feeder KTT</v>
+        <v>Trafo KTT SLFDO-1 (78 MVA), KTT PENI (40 MVA), KTT LCI (115 MVA), KTT MTSUI</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Peralatan (6)</v>
+        <v>6. Busbar (Rel Konduktor)</v>
       </c>
       <c r="B7" t="str">
-        <v>Busbar</v>
+        <v>busbar</v>
       </c>
       <c r="C7" t="str">
-        <v>Batang Rel Horizontal Tebal (Cyan/Biru)</v>
+        <v>Garis Horisontal Tebal: Biru (500 kV) atau Merah (150 kV)</v>
       </c>
       <c r="D7" t="str">
-        <v>Batang konduktor utama di Gardu Induk (GI / GITET) yang mengumpulkan dan membagikan daya listrik.</v>
+        <v>Rel konduktor pengumpul daya listrik di gardu induk. Dapat diset 'Normal' atau 'Panjang (Wide Busbar)' untuk membentang di atas beberapa bay.</v>
       </c>
       <c r="E7" t="str">
-        <v>Suralaya Baru (500 kV), GI SRLYA 150 kV, GI CLBRU 150 kV</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Peralatan (7)</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Beban</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Segitiga Terbalik (∇) Kuning Emas dengan terminal bulatan di atas</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Simbol resmi beban listrik konsumen industri KTT (Konsumen Tegangan Tinggi) atau feeder beban.</v>
-      </c>
-      <c r="E8" t="str">
-        <v>KTT SLFDO-1 (78 MVA), KTT PENI (40 MVA), KTT LCI (115 MVA)</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Peralatan (8)</v>
-      </c>
-      <c r="B9" t="str">
-        <v>PHT (Penghantar)</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Kapsul Saluran Transmisi dengan dua bulatan terminal di ujung</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Saluran udara/kabel transmisi tenaga listrik penghubung antar gardu induk.</v>
-      </c>
-      <c r="E9" t="str">
-        <v>PHT Suralaya - Salira Indah, PHT Suralaya - PENI</v>
+        <v>Rel 500 kV Suralaya Baru, Rel 150 kV SRLYA (Wide Busbar), Rel 150 kV CLBRU</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
+  <cols>
+    <col min="1" max="1" width="5.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="50.83203125" customWidth="1"/>
+    <col min="7" max="7" width="40.83203125" customWidth="1"/>
+    <col min="8" max="8" width="40.83203125" customWidth="1"/>
+    <col min="9" max="9" width="40.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3444,18 +4295,21 @@
         <v>Subsistem</v>
       </c>
       <c r="D1" t="str">
+        <v>Peralatan Terdampak</v>
+      </c>
+      <c r="E1" t="str">
         <v>UIT</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Kondisi / Permasalahan</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Dampak</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Mitigasi</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Usulan / Solusi</v>
       </c>
     </row>
@@ -3467,27 +4321,30 @@
         <v>1&amp;2</v>
       </c>
       <c r="C2" t="str">
-        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
+        <v>Suralaya - Cilegon</v>
       </c>
       <c r="D2" t="str">
-        <v>JBB</v>
+        <v>IBT 1 Suralaya &amp; IBT 2 Suralaya Baru (500/150 kV)</v>
       </c>
       <c r="E2" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="F2" t="str">
         <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
       </c>
-      <c r="F2" t="str" xml:space="preserve">
+      <c r="G2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
 2. Pertumbuhan beban menjadi terhambat.
 3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
       </c>
-      <c r="G2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025).
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025).
-3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit–3 beroperasi.</v>
-      </c>
       <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
+3. Pemeliharaan IBT saat beban rendah dan Unit 3 beroperasi.</v>
+      </c>
+      <c r="I2" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025/2026.</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -3498,26 +4355,27 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
+        <v>Suralaya - Cilegon</v>
       </c>
       <c r="D3" t="str">
-        <v>JBB</v>
+        <v>IBT 4 Cilegon Baru (500/150 kV)</v>
       </c>
       <c r="E3" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="F3" t="str">
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
       </c>
-      <c r="F3" t="str" xml:space="preserve">
+      <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
-2. Kondisi N–1–1 (IBT Suralaya dan IBT Cilegon) berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025).
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025).
-3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit–3 beroperasi.</v>
-      </c>
-      <c r="H3" t="str" xml:space="preserve">
+2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
+      </c>
+      <c r="I3" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2026.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -3528,30 +4386,33 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
+        <v>Suralaya - Cilegon</v>
       </c>
       <c r="D4" t="str">
-        <v>JBB</v>
+        <v>Ruas SUTT Suralaya–PENI, Suralaya–MCCI, MCCI–Cilegon, PENI–Mitsui–Cilegon</v>
       </c>
       <c r="E4" t="str">
+        <v>JBB</v>
+      </c>
+      <c r="F4" t="str">
         <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
       </c>
-      <c r="F4" t="str" xml:space="preserve">
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
 2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
       </c>
-      <c r="G4" t="str" xml:space="preserve">
+      <c r="H4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
 2. Pengaturan konfigurasi jaringan saat pemeliharaan untuk mengurangi dampak padam.</v>
       </c>
-      <c r="H4" t="str" xml:space="preserve">
+      <c r="I4" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Menengah :
 Usulan Double phi pada ruas Suralaya s.d Cilegon Lama (Kajian belum ada). Diusulkan COD Tahun 2030.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
+++ b/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
@@ -400,34 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y28"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
-    <col min="4" max="4" width="26.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
-    <col min="9" max="9" width="24.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
-    <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="15" max="15" width="16.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="24.83203125" customWidth="1"/>
-    <col min="18" max="18" width="24.83203125" customWidth="1"/>
-    <col min="19" max="19" width="22.83203125" customWidth="1"/>
-    <col min="20" max="20" width="22.83203125" customWidth="1"/>
-    <col min="21" max="21" width="10.83203125" customWidth="1"/>
-    <col min="22" max="22" width="45.83203125" customWidth="1"/>
-    <col min="23" max="23" width="35.83203125" customWidth="1"/>
-    <col min="24" max="24" width="35.83203125" customWidth="1"/>
-    <col min="25" max="25" width="35.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:Y21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -506,27 +479,27 @@
         <v>Usulan / Solusi</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>1&amp;2</v>
       </c>
       <c r="C2" t="str">
-        <v>Bay Evakuasi PLTU Suralaya Unit 3</v>
+        <v>Bay IBT 2 Suralaya Baru (500/150 kV)</v>
       </c>
       <c r="D2" t="str">
-        <v>Bay Generator &amp; GSUT</v>
+        <v>Bay IBT</v>
       </c>
       <c r="E2" t="str">
-        <v>trafo_generator</v>
+        <v>IBT</v>
       </c>
       <c r="F2" t="str">
-        <v>Unit 3</v>
+        <v>Suralaya Baru</v>
       </c>
       <c r="G2" t="str">
-        <v>generator</v>
+        <v>Busbar</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -535,13 +508,13 @@
         <v>SRLYA</v>
       </c>
       <c r="J2" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K2">
         <v>1</v>
       </c>
       <c r="L2" t="str">
-        <v>500 kV</v>
+        <v>500/150 kV</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -553,16 +526,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P2" t="str">
-        <v>Normal</v>
+        <v>Sangat Rawan</v>
       </c>
       <c r="Q2">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="R2" t="str">
         <v/>
       </c>
       <c r="S2">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T2" t="str">
         <v>Banten - Cilegon</v>
@@ -571,16 +544,21 @@
         <v>JBB</v>
       </c>
       <c r="V2" t="str">
-        <v>Bay Pembangkit Unit 3: 1. Generator (Hijau), 2. Trafo GSUT (Hijau-Merah), 3. CB PMT (Balok Merah)</v>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
+        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
+      </c>
+      <c r="W2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
+2. Pertumbuhan beban menjadi terhambat.
+3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
+      </c>
+      <c r="X2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW.
+3. Pemeliharaan IBT saat beban rendah.</v>
+      </c>
+      <c r="Y2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Jangka Pendek :
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025.</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -591,19 +569,19 @@
         <v>1&amp;2</v>
       </c>
       <c r="C3" t="str">
-        <v>Bay IBT 2 Suralaya Baru (500/150 kV)</v>
+        <v>Bay IBT 1 Suralaya (500/150 kV)</v>
       </c>
       <c r="D3" t="str">
-        <v>Bay Interbus Transformer</v>
+        <v>Bay IBT</v>
       </c>
       <c r="E3" t="str">
-        <v>ibt</v>
+        <v>IBT</v>
       </c>
       <c r="F3" t="str">
-        <v>Suralaya Baru</v>
+        <v>Suralaya</v>
       </c>
       <c r="G3" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -612,7 +590,7 @@
         <v>SRLYA</v>
       </c>
       <c r="J3" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -633,7 +611,7 @@
         <v>Sangat Rawan</v>
       </c>
       <c r="Q3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -648,21 +626,19 @@
         <v>JBB</v>
       </c>
       <c r="V3" t="str">
-        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
       </c>
       <c r="W3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
-2. Pertumbuhan beban menjadi terhambat.
-3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
+        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
+2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
       </c>
       <c r="X3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
-3. Pemeliharaan IBT saat beban rendah.</v>
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya.
+2. Pemeliharaan IBT saat beban rendah.</v>
       </c>
       <c r="Y3" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD Tahun 2025.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2026.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -670,31 +646,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>1&amp;2</v>
+        <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>Bay IBT 1 Suralaya (500/150 kV)</v>
+        <v>Bay IBT 4 Cilegon Baru (500/150 kV)</v>
       </c>
       <c r="D4" t="str">
-        <v>Bay Interbus Transformer</v>
+        <v>Bay IBT</v>
       </c>
       <c r="E4" t="str">
-        <v>ibt</v>
+        <v>IBT</v>
       </c>
       <c r="F4" t="str">
-        <v>Suralaya</v>
+        <v>Cilegon Baru</v>
       </c>
       <c r="G4" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4" t="str">
-        <v>SRLYA</v>
+        <v>CLBRU</v>
       </c>
       <c r="J4" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K4">
         <v>1</v>
@@ -715,7 +691,7 @@
         <v>Sangat Rawan</v>
       </c>
       <c r="Q4">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="R4" t="str">
         <v/>
@@ -730,57 +706,55 @@
         <v>JBB</v>
       </c>
       <c r="V4" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
-      </c>
-      <c r="W4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
-2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="X4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Pemeliharaan IBT saat beban rendah dan Unit 3 beroperasi.</v>
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama.</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
       </c>
       <c r="Y4" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD Tahun 2026.</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA.</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="C5" t="str">
-        <v>Bay IBT 4 Cilegon Baru (500/150 kV)</v>
+        <v>Bay Evakuasi Unit 3 PLTU Suralaya</v>
       </c>
       <c r="D5" t="str">
-        <v>Bay Interbus Transformer</v>
+        <v>Bay Generator</v>
       </c>
       <c r="E5" t="str">
-        <v>ibt</v>
+        <v>Trafo Generator</v>
       </c>
       <c r="F5" t="str">
-        <v>Cilegon Baru</v>
+        <v>Unit 3</v>
       </c>
       <c r="G5" t="str">
-        <v>busbar</v>
+        <v>Pembangkit</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5" t="str">
-        <v>CLBRU</v>
+        <v>SRLYA</v>
       </c>
       <c r="J5" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="str">
-        <v>500/150 kV</v>
+        <v>500 kV</v>
       </c>
       <c r="M5">
         <v>1</v>
@@ -792,16 +766,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P5" t="str">
-        <v>Sangat Rawan</v>
+        <v>Normal</v>
       </c>
       <c r="Q5">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="str">
         <v>Banten - Cilegon</v>
@@ -810,17 +784,16 @@
         <v>JBB</v>
       </c>
       <c r="V5" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #4 Cilegon 500 MVA sedangkan IBT #1,2 Suralaya 250 MVA).</v>
+        <v>Evakuasi daya PLTU Suralaya Unit 3 (1. Pembangkit, 2. Trafo Step-Up, 3. CB).</v>
       </c>
       <c r="W5" t="str">
-        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+        <v/>
       </c>
       <c r="X5" t="str">
-        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
-      </c>
-      <c r="Y5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2026.</v>
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -831,19 +804,19 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>SUTT 150 kV SRLYA - SLRDA</v>
+        <v>Suralaya - Salira Indah (Sirkit 1)</v>
       </c>
       <c r="D6" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E6" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F6" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G6" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -852,7 +825,7 @@
         <v>SLRDA</v>
       </c>
       <c r="J6" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -861,7 +834,7 @@
         <v>150 kV</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -873,13 +846,13 @@
         <v>Normal</v>
       </c>
       <c r="Q6">
-        <v>54</v>
-      </c>
-      <c r="R6" t="str">
-        <v/>
+        <v>52</v>
+      </c>
+      <c r="R6">
+        <v>48</v>
       </c>
       <c r="S6">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="T6" t="str">
         <v>Banten - Cilegon</v>
@@ -908,28 +881,28 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>SUTT 150 kV SRLYA - PENDO</v>
+        <v>Suralaya - Salira Indah (Sirkit 2)</v>
       </c>
       <c r="D7" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E7" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F7" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G7" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>PENDO</v>
+        <v>SLRDA</v>
       </c>
       <c r="J7" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -938,10 +911,10 @@
         <v>150 kV</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="str">
         <v>Beroperasi</v>
@@ -950,13 +923,13 @@
         <v>Normal</v>
       </c>
       <c r="Q7">
+        <v>52</v>
+      </c>
+      <c r="R7">
         <v>48</v>
       </c>
-      <c r="R7" t="str">
-        <v/>
-      </c>
       <c r="S7">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="T7" t="str">
         <v>Banten - Cilegon</v>
@@ -985,19 +958,19 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>SUTT 150 kV Tie Line SLRDA - PENDO</v>
+        <v>Salira Indah - Pendo</v>
       </c>
       <c r="D8" t="str">
-        <v>Tie Line Interkoneksi</v>
+        <v>PHT</v>
       </c>
       <c r="E8" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F8" t="str">
         <v>SLRDA</v>
       </c>
       <c r="G8" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1006,7 +979,7 @@
         <v>PENDO</v>
       </c>
       <c r="J8" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K8">
         <v>2</v>
@@ -1027,13 +1000,13 @@
         <v>Normal</v>
       </c>
       <c r="Q8">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="T8" t="str">
         <v>Banten - Cilegon</v>
@@ -1042,7 +1015,7 @@
         <v>JBB</v>
       </c>
       <c r="V8" t="str">
-        <v>Interkoneksi antar bay busbar Salira Indah (SLRDA) dan Pendo (PENDO) di Tier 2.</v>
+        <v/>
       </c>
       <c r="W8" t="str">
         <v/>
@@ -1054,7 +1027,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" xml:space="preserve">
+    <row r="9">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1062,19 +1035,19 @@
         <v>3</v>
       </c>
       <c r="C9" t="str">
-        <v>SUTT 150 kV SRLYA - PENI</v>
+        <v>Suralaya - Chandra Asri (PENI)</v>
       </c>
       <c r="D9" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E9" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F9" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G9" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1083,7 +1056,7 @@
         <v>PENI</v>
       </c>
       <c r="J9" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K9">
         <v>2</v>
@@ -1104,13 +1077,13 @@
         <v>N-1</v>
       </c>
       <c r="Q9">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9">
-        <v>18.5</v>
+        <v>15.2</v>
       </c>
       <c r="T9" t="str">
         <v>Banten - Cilegon</v>
@@ -1119,22 +1092,19 @@
         <v>JBB</v>
       </c>
       <c r="V9" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
-      </c>
-      <c r="W9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
-2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
-      </c>
-      <c r="X9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
-2. Pengaturan konfigurasi jaringan saat pemeliharaan untuk mengurangi dampak padam.</v>
-      </c>
-      <c r="Y9" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Menengah :
-Usulan Double phi pada ruas Suralaya s.d Cilegon Lama (Kajian belum ada). Diusulkan COD Tahun 2030.</v>
-      </c>
-    </row>
-    <row r="10" xml:space="preserve">
+        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Penyesuaian jadwal pemeliharaan.</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Double phi COD 2030.</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1142,19 +1112,19 @@
         <v>3</v>
       </c>
       <c r="C10" t="str">
-        <v>SUTT 150 kV SRLYA - MCCI5</v>
+        <v>Suralaya - MCCI</v>
       </c>
       <c r="D10" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E10" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F10" t="str">
         <v>SRLYA</v>
       </c>
       <c r="G10" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1163,7 +1133,7 @@
         <v>MCCI5</v>
       </c>
       <c r="J10" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -1184,13 +1154,13 @@
         <v>N-1</v>
       </c>
       <c r="Q10">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10">
-        <v>16.3</v>
+        <v>16.8</v>
       </c>
       <c r="T10" t="str">
         <v>Banten - Cilegon</v>
@@ -1199,60 +1169,57 @@
         <v>JBB</v>
       </c>
       <c r="V10" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
-      </c>
-      <c r="W10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
-2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
-      </c>
-      <c r="X10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
-2. Pengaturan konfigurasi jaringan saat pemeliharaan.</v>
-      </c>
-      <c r="Y10" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Menengah :
-Usulan Double phi pada ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
-      </c>
-    </row>
-    <row r="11" xml:space="preserve">
+        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Pemadaman apabila terjadi trip.</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="C11" t="str">
-        <v>SUTT 150 kV PENI - MTSUI</v>
+        <v>Cilegon Baru - Cilegon Lama (Sirkit 1)</v>
       </c>
       <c r="D11" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E11" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F11" t="str">
-        <v>PENI</v>
+        <v>CLBRU</v>
       </c>
       <c r="G11" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11" t="str">
+        <v>CLGON</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K11">
         <v>2</v>
-      </c>
-      <c r="I11" t="str">
-        <v>MTSUI</v>
-      </c>
-      <c r="J11" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="K11">
-        <v>3</v>
       </c>
       <c r="L11" t="str">
         <v>150 kV</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1261,16 +1228,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P11" t="str">
-        <v>N-1</v>
+        <v>Normal</v>
       </c>
       <c r="Q11">
-        <v>68</v>
-      </c>
-      <c r="R11" t="str">
-        <v/>
+        <v>54</v>
+      </c>
+      <c r="R11">
+        <v>50</v>
       </c>
       <c r="S11">
-        <v>8.7</v>
+        <v>9.2</v>
       </c>
       <c r="T11" t="str">
         <v>Banten - Cilegon</v>
@@ -1279,18 +1246,16 @@
         <v>JBB</v>
       </c>
       <c r="V11" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
-      </c>
-      <c r="W11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
-2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
+        <v/>
+      </c>
+      <c r="W11" t="str">
+        <v/>
       </c>
       <c r="X11" t="str">
-        <v>1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.</v>
-      </c>
-      <c r="Y11" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Menengah :
-Usulan Double phi pada ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
+        <v/>
+      </c>
+      <c r="Y11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1298,31 +1263,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="C12" t="str">
-        <v>SUTT 150 kV MCCI5 - CLGON</v>
+        <v>Cilegon Baru - Cilegon Lama (Sirkit 2)</v>
       </c>
       <c r="D12" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E12" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F12" t="str">
-        <v>MCCI5</v>
+        <v>CLBRU</v>
       </c>
       <c r="G12" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
         <v>CLGON</v>
       </c>
       <c r="J12" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -1331,25 +1296,25 @@
         <v>150 kV</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="str">
         <v>Beroperasi</v>
       </c>
       <c r="P12" t="str">
-        <v>N-1</v>
+        <v>Normal</v>
       </c>
       <c r="Q12">
-        <v>65</v>
-      </c>
-      <c r="R12" t="str">
-        <v/>
+        <v>54</v>
+      </c>
+      <c r="R12">
+        <v>50</v>
       </c>
       <c r="S12">
-        <v>9.4</v>
+        <v>9.2</v>
       </c>
       <c r="T12" t="str">
         <v>Banten - Cilegon</v>
@@ -1358,16 +1323,16 @@
         <v>JBB</v>
       </c>
       <c r="V12" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+        <v/>
       </c>
       <c r="W12" t="str">
-        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
+        <v/>
       </c>
       <c r="X12" t="str">
-        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
+        <v/>
       </c>
       <c r="Y12" t="str">
-        <v>Usulan double phi ruas Suralaya s.d Cilegon Lama. COD Tahun 2030.</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1378,31 +1343,31 @@
         <v>3</v>
       </c>
       <c r="C13" t="str">
-        <v>SUTT 150 kV MTSUI - CLGON</v>
+        <v>Chandra Asri (PENI) - Mitsui (MTSUI)</v>
       </c>
       <c r="D13" t="str">
-        <v>Saluran Udara (SUTT)</v>
+        <v>PHT</v>
       </c>
       <c r="E13" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F13" t="str">
+        <v>PENI</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H13">
+        <v>2</v>
+      </c>
+      <c r="I13" t="str">
         <v>MTSUI</v>
       </c>
-      <c r="G13" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H13">
+      <c r="J13" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="K13">
         <v>3</v>
-      </c>
-      <c r="I13" t="str">
-        <v>CLGON</v>
-      </c>
-      <c r="J13" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="K13">
-        <v>2</v>
       </c>
       <c r="L13" t="str">
         <v>150 kV</v>
@@ -1420,13 +1385,13 @@
         <v>N-1</v>
       </c>
       <c r="Q13">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="T13" t="str">
         <v>Banten - Cilegon</v>
@@ -1435,16 +1400,16 @@
         <v>JBB</v>
       </c>
       <c r="V13" t="str">
-        <v>Ruas Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
+        <v>Ruas Peni-Mitsui-Cilegon masih single phi.</v>
       </c>
       <c r="W13" t="str">
-        <v>Pemadaman apabila terjadi gangguan N-1.</v>
+        <v>Pemadaman apabila trip.</v>
       </c>
       <c r="X13" t="str">
-        <v>Pengaturan konfigurasi jaringan sistem Banten.</v>
+        <v>Jadwal pemeliharaan KTT.</v>
       </c>
       <c r="Y13" t="str">
-        <v>Double phi ruas Suralaya s.d Cilegon Lama.</v>
+        <v>Usulan double phi COD 2030.</v>
       </c>
     </row>
     <row r="14">
@@ -1455,28 +1420,28 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>SUTT 150 kV CLBRU - CLGON Sirkit 1</v>
+        <v>Mitsui (MTSUI) - Cilegon Lama</v>
       </c>
       <c r="D14" t="str">
-        <v>Double Circuit Line 1</v>
+        <v>PHT</v>
       </c>
       <c r="E14" t="str">
-        <v>cb</v>
+        <v>PHT</v>
       </c>
       <c r="F14" t="str">
-        <v>CLBRU</v>
+        <v>MTSUI</v>
       </c>
       <c r="G14" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="str">
         <v>CLGON</v>
       </c>
       <c r="J14" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -1485,7 +1450,7 @@
         <v>150 kV</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1497,13 +1462,13 @@
         <v>Normal</v>
       </c>
       <c r="Q14">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14">
-        <v>11.2</v>
+        <v>5.4</v>
       </c>
       <c r="T14" t="str">
         <v>Banten - Cilegon</v>
@@ -1512,7 +1477,7 @@
         <v>JBB</v>
       </c>
       <c r="V14" t="str">
-        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 1.</v>
+        <v/>
       </c>
       <c r="W14" t="str">
         <v/>
@@ -1532,40 +1497,40 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>SUTT 150 kV CLBRU - CLGON Sirkit 2</v>
+        <v>Feeder Beban KTT SLFDO-1 (78 MVA)</v>
       </c>
       <c r="D15" t="str">
-        <v>Double Circuit Line 2</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E15" t="str">
-        <v>cb</v>
+        <v>Beban</v>
       </c>
       <c r="F15" t="str">
-        <v>CLBRU</v>
+        <v>SLRDA</v>
       </c>
       <c r="G15" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="str">
-        <v>CLGON</v>
+        <v>KTT SLFDO-1</v>
       </c>
       <c r="J15" t="str">
-        <v>busbar</v>
+        <v>Beban</v>
       </c>
       <c r="K15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" t="str">
-        <v>150 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="str">
         <v>Beroperasi</v>
@@ -1574,13 +1539,13 @@
         <v>Normal</v>
       </c>
       <c r="Q15">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="T15" t="str">
         <v>Banten - Cilegon</v>
@@ -1589,7 +1554,7 @@
         <v>JBB</v>
       </c>
       <c r="V15" t="str">
-        <v>Jalur ganda menghubungkan Cilegon Baru dan Cilegon Lama Sirkit 2.</v>
+        <v>Feeder Konsumen Industri KTT SLFDO-1</v>
       </c>
       <c r="W15" t="str">
         <v/>
@@ -1609,34 +1574,34 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Bay Trafo Distribusi SRLYA</v>
+        <v>Feeder Beban KTT SLFDO-2 (30 MVA)</v>
       </c>
       <c r="D16" t="str">
-        <v>Bay Trafo</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E16" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="F16" t="str">
-        <v>SRLYA</v>
+        <v>SLRDA</v>
       </c>
       <c r="G16" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="str">
-        <v>Trafo Distribusi SRLYA</v>
+        <v>KTT SLFDO-2</v>
       </c>
       <c r="J16" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M16">
         <v>1</v>
@@ -1651,13 +1616,13 @@
         <v>Normal</v>
       </c>
       <c r="Q16">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16">
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="str">
         <v>Banten - Cilegon</v>
@@ -1666,7 +1631,7 @@
         <v>JBB</v>
       </c>
       <c r="V16" t="str">
-        <v>Trafo pemakaian sendiri / distribusi lokal 150/20 kV Suralaya.</v>
+        <v>Feeder Konsumen Industri KTT SLFDO-2</v>
       </c>
       <c r="W16" t="str">
         <v/>
@@ -1686,34 +1651,34 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Bay Trafo Distribusi CLBRU</v>
+        <v>Feeder Beban KTT PENDO (35 MVA)</v>
       </c>
       <c r="D17" t="str">
-        <v>Bay Trafo</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E17" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="F17" t="str">
-        <v>CLBRU</v>
+        <v>PENDO</v>
       </c>
       <c r="G17" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="str">
-        <v>Trafo Distribusi CLBRU</v>
+        <v>KTT PENDO</v>
       </c>
       <c r="J17" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -1728,13 +1693,13 @@
         <v>Normal</v>
       </c>
       <c r="Q17">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="T17" t="str">
         <v>Banten - Cilegon</v>
@@ -1743,7 +1708,7 @@
         <v>JBB</v>
       </c>
       <c r="V17" t="str">
-        <v>Trafo distribusi lokal 150/20 kV Cilegon Baru.</v>
+        <v>Feeder Konsumen Industri KTT PENDO</v>
       </c>
       <c r="W17" t="str">
         <v/>
@@ -1760,37 +1725,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="C18" t="str">
-        <v>Feeder Trafo SLRDA ke KTT SLFDO-1</v>
+        <v>Feeder Beban KTT PENI (40 MVA)</v>
       </c>
       <c r="D18" t="str">
-        <v>Feeder KTT</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E18" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="F18" t="str">
-        <v>SLRDA</v>
+        <v>PENI</v>
       </c>
       <c r="G18" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H18">
         <v>2</v>
       </c>
       <c r="I18" t="str">
-        <v>KTT SLFDO-1</v>
+        <v>KTT PENI</v>
       </c>
       <c r="J18" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K18">
         <v>3</v>
       </c>
       <c r="L18" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M18">
         <v>1</v>
@@ -1802,16 +1767,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P18" t="str">
-        <v>Normal</v>
+        <v>N-1</v>
       </c>
       <c r="Q18">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="T18" t="str">
         <v>Banten - Cilegon</v>
@@ -1820,7 +1785,7 @@
         <v>JBB</v>
       </c>
       <c r="V18" t="str">
-        <v>Suplai konsumen KTT SLFDO-1 Kapasitas 78 MVA</v>
+        <v>Feeder Konsumen Industri KTT PENI</v>
       </c>
       <c r="W18" t="str">
         <v/>
@@ -1840,37 +1805,37 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Feeder Trafo SLRDA ke KTT SLFDO-2</v>
+        <v>Feeder Beban KTT LCI (115 MVA)</v>
       </c>
       <c r="D19" t="str">
-        <v>Feeder KTT</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E19" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="F19" t="str">
-        <v>SLRDA</v>
+        <v>PENI</v>
       </c>
       <c r="G19" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H19">
         <v>2</v>
       </c>
       <c r="I19" t="str">
-        <v>KTT SLFDO-2</v>
+        <v>KTT LCI</v>
       </c>
       <c r="J19" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K19">
         <v>3</v>
       </c>
       <c r="L19" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -1882,13 +1847,13 @@
         <v>Normal</v>
       </c>
       <c r="Q19">
-        <v>65</v>
-      </c>
-      <c r="R19" t="str">
-        <v/>
+        <v>58</v>
+      </c>
+      <c r="R19">
+        <v>57</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T19" t="str">
         <v>Banten - Cilegon</v>
@@ -1897,7 +1862,7 @@
         <v>JBB</v>
       </c>
       <c r="V19" t="str">
-        <v>Suplai konsumen KTT SLFDO-2 Kapasitas 30 MVA</v>
+        <v>Feeder Konsumen Industri KTT LCI</v>
       </c>
       <c r="W19" t="str">
         <v/>
@@ -1917,34 +1882,34 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Feeder Trafo PENDO ke KTT PENDO</v>
+        <v>Feeder Beban KTT MCCI (40 MVA)</v>
       </c>
       <c r="D20" t="str">
-        <v>Feeder KTT</v>
+        <v>Feeder Beban</v>
       </c>
       <c r="E20" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="F20" t="str">
-        <v>PENDO</v>
+        <v>MCCI5</v>
       </c>
       <c r="G20" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="H20">
         <v>2</v>
       </c>
       <c r="I20" t="str">
-        <v>KTT PENDO</v>
+        <v>KTT MCCI</v>
       </c>
       <c r="J20" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K20">
         <v>3</v>
       </c>
       <c r="L20" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M20">
         <v>1</v>
@@ -1959,13 +1924,13 @@
         <v>Normal</v>
       </c>
       <c r="Q20">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T20" t="str">
         <v>Banten - Cilegon</v>
@@ -1974,7 +1939,7 @@
         <v>JBB</v>
       </c>
       <c r="V20" t="str">
-        <v>Suplai konsumen KTT PENDO Kapasitas 35 MVA</v>
+        <v>Feeder Konsumen Industri KTT MCCI</v>
       </c>
       <c r="W20" t="str">
         <v/>
@@ -1991,37 +1956,37 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
+        <v/>
+      </c>
+      <c r="C21" t="str">
+        <v>Feeder Beban KTT MTSUI (31 MVA)</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Feeder Beban</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="F21" t="str">
+        <v>MTSUI</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Busbar</v>
+      </c>
+      <c r="H21">
         <v>3</v>
       </c>
-      <c r="C21" t="str">
-        <v>Feeder Trafo PENI ke KTT PENI</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Feeder KTT</v>
-      </c>
-      <c r="E21" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PENI</v>
-      </c>
-      <c r="G21" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H21">
-        <v>2</v>
-      </c>
       <c r="I21" t="str">
-        <v>KTT PENI</v>
+        <v>KTT MTSUI</v>
       </c>
       <c r="J21" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L21" t="str">
-        <v>150/20 kV</v>
+        <v>20 kV</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -2033,16 +1998,16 @@
         <v>Beroperasi</v>
       </c>
       <c r="P21" t="str">
-        <v>N-1</v>
+        <v>Normal</v>
       </c>
       <c r="Q21">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="T21" t="str">
         <v>Banten - Cilegon</v>
@@ -2051,586 +2016,28 @@
         <v>JBB</v>
       </c>
       <c r="V21" t="str">
-        <v>Suplai konsumen KTT PENI Chandra Asri Kapasitas 40 MVA</v>
+        <v>Feeder Konsumen Industri KTT Mitsui</v>
       </c>
       <c r="W21" t="str">
-        <v>Terdapat risiko suplai saat pemeliharaan ruas single phi.</v>
+        <v/>
       </c>
       <c r="X21" t="str">
-        <v>Penyesuaian jadwal dengan konsumen industri.</v>
+        <v/>
       </c>
       <c r="Y21" t="str">
-        <v>Usulan double phi transmisi 150 kV.</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v/>
-      </c>
-      <c r="C22" t="str">
-        <v>Feeder Trafo PENI ke KTT LCI</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Feeder KTT</v>
-      </c>
-      <c r="E22" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PENI</v>
-      </c>
-      <c r="G22" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H22">
-        <v>2</v>
-      </c>
-      <c r="I22" t="str">
-        <v>KTT LCI</v>
-      </c>
-      <c r="J22" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="M22">
-        <v>2</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="P22" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q22">
-        <v>64</v>
-      </c>
-      <c r="R22" t="str">
-        <v/>
-      </c>
-      <c r="S22">
-        <v>1.5</v>
-      </c>
-      <c r="T22" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U22" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V22" t="str">
-        <v>Suplai 2 sirkit konsumen KTT LCI Kapasitas 115 MVA</v>
-      </c>
-      <c r="W22" t="str">
-        <v/>
-      </c>
-      <c r="X22" t="str">
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v>Feeder Trafo MCCI5 ke KTT MCCI</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Feeder KTT</v>
-      </c>
-      <c r="E23" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="F23" t="str">
-        <v>MCCI5</v>
-      </c>
-      <c r="G23" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H23">
-        <v>2</v>
-      </c>
-      <c r="I23" t="str">
-        <v>KTT MCCI</v>
-      </c>
-      <c r="J23" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="K23">
-        <v>3</v>
-      </c>
-      <c r="L23" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="P23" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q23">
-        <v>55</v>
-      </c>
-      <c r="R23" t="str">
-        <v/>
-      </c>
-      <c r="S23">
-        <v>0.9</v>
-      </c>
-      <c r="T23" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U23" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V23" t="str">
-        <v>Suplai konsumen KTT MCCI Kapasitas 40 MVA</v>
-      </c>
-      <c r="W23" t="str">
-        <v/>
-      </c>
-      <c r="X23" t="str">
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v>Bay Trafo Distribusi CLGON</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Bay Trafo</v>
-      </c>
-      <c r="E24" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="F24" t="str">
-        <v>CLGON</v>
-      </c>
-      <c r="G24" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H24">
-        <v>2</v>
-      </c>
-      <c r="I24" t="str">
-        <v>Trafo Distribusi CLGON</v>
-      </c>
-      <c r="J24" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="K24">
-        <v>3</v>
-      </c>
-      <c r="L24" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="P24" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q24">
-        <v>52</v>
-      </c>
-      <c r="R24" t="str">
-        <v/>
-      </c>
-      <c r="S24">
-        <v>0.1</v>
-      </c>
-      <c r="T24" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U24" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V24" t="str">
-        <v>Trafo distribusi lokal 150/20 kV Cilegon Lama.</v>
-      </c>
-      <c r="W24" t="str">
-        <v/>
-      </c>
-      <c r="X24" t="str">
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v>Feeder Trafo MTSUI ke KTT MTSUI</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Feeder KTT</v>
-      </c>
-      <c r="E25" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="F25" t="str">
-        <v>MTSUI</v>
-      </c>
-      <c r="G25" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H25">
-        <v>3</v>
-      </c>
-      <c r="I25" t="str">
-        <v>KTT MTSUI</v>
-      </c>
-      <c r="J25" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="K25">
-        <v>4</v>
-      </c>
-      <c r="L25" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25" t="str">
-        <v>Beroperasi</v>
-      </c>
-      <c r="P25" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q25">
-        <v>50</v>
-      </c>
-      <c r="R25" t="str">
-        <v/>
-      </c>
-      <c r="S25">
-        <v>0.7</v>
-      </c>
-      <c r="T25" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U25" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V25" t="str">
-        <v>Suplai konsumen KTT MTSUI Kapasitas 31 MVA</v>
-      </c>
-      <c r="W25" t="str">
-        <v/>
-      </c>
-      <c r="X25" t="str">
-        <v/>
-      </c>
-      <c r="Y25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v>Bay Feeder CLBRU ke KSTEL (Rencana)</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Bay Rencana</v>
-      </c>
-      <c r="E26" t="str">
-        <v>cb</v>
-      </c>
-      <c r="F26" t="str">
-        <v>CLBRU</v>
-      </c>
-      <c r="G26" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26" t="str">
-        <v>KSTEL</v>
-      </c>
-      <c r="J26" t="str">
-        <v>cb</v>
-      </c>
-      <c r="K26">
-        <v>3</v>
-      </c>
-      <c r="L26" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26" t="str">
-        <v>Rencana</v>
-      </c>
-      <c r="P26" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26" t="str">
-        <v/>
-      </c>
-      <c r="S26">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U26" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V26" t="str">
-        <v>Bay Rencana Penghantar KSTEL (Dashed Line)</v>
-      </c>
-      <c r="W26" t="str">
-        <v/>
-      </c>
-      <c r="X26" t="str">
-        <v/>
-      </c>
-      <c r="Y26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v>Bay Feeder CLBRU ke POSCO (Rencana)</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Bay Rencana</v>
-      </c>
-      <c r="E27" t="str">
-        <v>cb</v>
-      </c>
-      <c r="F27" t="str">
-        <v>CLBRU</v>
-      </c>
-      <c r="G27" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27" t="str">
-        <v>POSCO</v>
-      </c>
-      <c r="J27" t="str">
-        <v>cb</v>
-      </c>
-      <c r="K27">
-        <v>3</v>
-      </c>
-      <c r="L27" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27" t="str">
-        <v>Rencana</v>
-      </c>
-      <c r="P27" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27" t="str">
-        <v/>
-      </c>
-      <c r="S27">
-        <v>4.2</v>
-      </c>
-      <c r="T27" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U27" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V27" t="str">
-        <v>Bay Rencana Penghantar POSCO (Dashed Line)</v>
-      </c>
-      <c r="W27" t="str">
-        <v/>
-      </c>
-      <c r="X27" t="str">
-        <v/>
-      </c>
-      <c r="Y27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v>Bay Feeder CLGON ke KSTEL (Rencana)</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Bay Rencana</v>
-      </c>
-      <c r="E28" t="str">
-        <v>cb</v>
-      </c>
-      <c r="F28" t="str">
-        <v>CLGON</v>
-      </c>
-      <c r="G28" t="str">
-        <v>busbar</v>
-      </c>
-      <c r="H28">
-        <v>2</v>
-      </c>
-      <c r="I28" t="str">
-        <v>KSTEL</v>
-      </c>
-      <c r="J28" t="str">
-        <v>cb</v>
-      </c>
-      <c r="K28">
-        <v>3</v>
-      </c>
-      <c r="L28" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28" t="str">
-        <v>Rencana</v>
-      </c>
-      <c r="P28" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28" t="str">
-        <v/>
-      </c>
-      <c r="S28">
-        <v>2.8</v>
-      </c>
-      <c r="T28" t="str">
-        <v>Banten - Cilegon</v>
-      </c>
-      <c r="U28" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="V28" t="str">
-        <v>Bay Rencana Penghantar KSTEL dari CLGON (Dashed Line)</v>
-      </c>
-      <c r="W28" t="str">
-        <v/>
-      </c>
-      <c r="X28" t="str">
-        <v/>
-      </c>
-      <c r="Y28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q28"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.83203125" customWidth="1"/>
-    <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="45.83203125" customWidth="1"/>
-    <col min="15" max="15" width="35.83203125" customWidth="1"/>
-    <col min="16" max="16" width="35.83203125" customWidth="1"/>
-    <col min="17" max="17" width="35.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:Q25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2696,10 +2103,10 @@
         <v>Suralaya Baru</v>
       </c>
       <c r="D2" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E2" t="str">
-        <v>Panjang (Wide Busbar)</v>
+        <v>Normal</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -2726,7 +2133,7 @@
         <v>JBB</v>
       </c>
       <c r="N2" t="str">
-        <v>Rel Busbar 500 kV Suralaya Baru (Warna Biru)</v>
+        <v>Busbar 500 kV Suralaya Baru</v>
       </c>
       <c r="O2" t="str">
         <v/>
@@ -2749,10 +2156,10 @@
         <v>Suralaya</v>
       </c>
       <c r="D3" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E3" t="str">
-        <v>Panjang (Wide Busbar)</v>
+        <v>Normal</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -2779,7 +2186,7 @@
         <v>JBB</v>
       </c>
       <c r="N3" t="str">
-        <v>Rel Busbar 500 kV Suralaya (Warna Biru)</v>
+        <v>Busbar 500 kV Suralaya</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -2802,10 +2209,10 @@
         <v>Cilegon Baru</v>
       </c>
       <c r="D4" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E4" t="str">
-        <v>Panjang (Wide Busbar)</v>
+        <v>Normal</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -2832,7 +2239,7 @@
         <v>JBB</v>
       </c>
       <c r="N4" t="str">
-        <v>Rel Busbar 500 kV Cilegon Baru (Warna Biru)</v>
+        <v>Busbar 500 kV Cilegon Baru</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -2855,7 +2262,7 @@
         <v>Unit 3</v>
       </c>
       <c r="D5" t="str">
-        <v>generator</v>
+        <v>Pembangkit</v>
       </c>
       <c r="E5" t="str">
         <v>Normal</v>
@@ -2885,7 +2292,7 @@
         <v>JBB</v>
       </c>
       <c r="N5" t="str">
-        <v>Generator Pembangkit Unit 3 (Lingkaran Hijau + Simbol AC ~) dengan Step-up GSUT</v>
+        <v>Bay Pembangkit: 1. Pembangkit, 2. Trafo Generator, 3. CB</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -2897,7 +2304,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" xml:space="preserve">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2908,7 +2315,7 @@
         <v>IBT 2 SRL-BARU</v>
       </c>
       <c r="D6" t="str">
-        <v>ibt</v>
+        <v>IBT</v>
       </c>
       <c r="E6" t="str">
         <v>Normal</v>
@@ -2938,24 +2345,19 @@
         <v>JBB</v>
       </c>
       <c r="N6" t="str">
-        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
-      </c>
-      <c r="O6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
-2. Pertumbuhan beban menjadi terhambat.
-3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
-      </c>
-      <c r="P6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
-3. Pemeliharaan IBT saat beban rendah.</v>
-      </c>
-      <c r="Q6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2025.</v>
-      </c>
-    </row>
-    <row r="7" xml:space="preserve">
+        <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi.</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Pemadaman apabila trip salah satu IBT.</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Terpasang DS OLS IBT 1,2 Suralaya.</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Uprating IBT–1 &amp; 2 dari 250 MVA menjadi 500 MVA.</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2966,7 +2368,7 @@
         <v>IBT 1 SRLYA</v>
       </c>
       <c r="D7" t="str">
-        <v>ibt</v>
+        <v>IBT</v>
       </c>
       <c r="E7" t="str">
         <v>Normal</v>
@@ -2996,22 +2398,19 @@
         <v>JBB</v>
       </c>
       <c r="N7" t="str">
-        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
-      </c>
-      <c r="O7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
-2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="P7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya.
-2. Pemeliharaan IBT saat beban rendah.</v>
-      </c>
-      <c r="Q7" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. COD Tahun 2026.</v>
-      </c>
-    </row>
-    <row r="8" xml:space="preserve">
+        <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA).</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Overload pada IBT Suralaya.</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Terpasang DS OLS IBT 1,2 Suralaya.</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Uprating IBT–1 &amp; 2 dari 250 MVA menjadi 500 MVA.</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3022,7 +2421,7 @@
         <v>IBT 4 CLBRU</v>
       </c>
       <c r="D8" t="str">
-        <v>ibt</v>
+        <v>IBT</v>
       </c>
       <c r="E8" t="str">
         <v>Normal</v>
@@ -3055,14 +2454,13 @@
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #4 Cilegon 500 MVA).</v>
       </c>
       <c r="O8" t="str">
-        <v>Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
+        <v>Ketidakseimbangan beban.</v>
       </c>
       <c r="P8" t="str">
-        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
-      </c>
-      <c r="Q8" t="str" xml:space="preserve">
-        <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya menjadi 500 MVA.</v>
+        <v>Optimalisasi transfer trip antar GI.</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>Uprating IBT–1 &amp; 2 Suralaya menjadi 500 MVA.</v>
       </c>
     </row>
     <row r="9">
@@ -3070,13 +2468,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Gardu Induk SRLYA (150 kV)</v>
+        <v>GI Suralaya 150 kV (Rel Busbar)</v>
       </c>
       <c r="C9" t="str">
         <v>SRLYA</v>
       </c>
       <c r="D9" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E9" t="str">
         <v>Panjang (Wide Busbar)</v>
@@ -3106,7 +2504,7 @@
         <v>JBB</v>
       </c>
       <c r="N9" t="str">
-        <v>Busbar Utama 150 kV Suralaya (Tier 1, Merah Panjang menampung Unit 3, IBT 1, IBT 2, dan 5 Saluran ke Bawah)</v>
+        <v>Busbar 150 kV Suralaya (Menghubungkan IBT 1, IBT 2, dan Saluran Distribusi)</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -3123,13 +2521,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Gardu Induk CLBRU (150 kV)</v>
+        <v>GI Cilegon Baru 150 kV (Rel Busbar)</v>
       </c>
       <c r="C10" t="str">
         <v>CLBRU</v>
       </c>
       <c r="D10" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E10" t="str">
         <v>Panjang (Wide Busbar)</v>
@@ -3159,7 +2557,7 @@
         <v>JBB</v>
       </c>
       <c r="N10" t="str">
-        <v>Busbar Utama 150 kV Cilegon Baru (Tier 1, Merah Panjang menghubungkan IBT 4 ke CLGON, Trafo Lokal, KSTEL, POSCO)</v>
+        <v>Busbar 150 kV Cilegon Baru</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -3176,13 +2574,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Gardu Induk SLRDA (150 kV)</v>
+        <v>GI Salira Indah</v>
       </c>
       <c r="C11" t="str">
         <v>SLRDA</v>
       </c>
       <c r="D11" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E11" t="str">
         <v>Normal</v>
@@ -3212,7 +2610,7 @@
         <v>JBB</v>
       </c>
       <c r="N11" t="str">
-        <v>Gardu Induk Salira Indah (Tier 2, Menyuplai KTT SLFDO-1 &amp; SLFDO-2)</v>
+        <v>Gardu Induk Salira Indah</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -3229,13 +2627,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Gardu Induk PENDO (150 kV)</v>
+        <v>GI Pendo</v>
       </c>
       <c r="C12" t="str">
         <v>PENDO</v>
       </c>
       <c r="D12" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E12" t="str">
         <v>Normal</v>
@@ -3265,7 +2663,7 @@
         <v>JBB</v>
       </c>
       <c r="N12" t="str">
-        <v>Gardu Induk Pendo (Tier 2, Menyuplai KTT PENDO 35 MVA)</v>
+        <v>Gardu Induk Pendo</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -3282,13 +2680,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Gardu Induk PENI (150 kV)</v>
+        <v>GI Chandra Asri (PENI)</v>
       </c>
       <c r="C13" t="str">
         <v>PENI</v>
       </c>
       <c r="D13" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E13" t="str">
         <v>Normal</v>
@@ -3318,16 +2716,16 @@
         <v>JBB</v>
       </c>
       <c r="N13" t="str">
-        <v>Ruas Penghantar Suralaya–PENI–Mitsui–Cilegon masih single phi.</v>
+        <v>Ruas Penghantar Suralaya-PENI masih single phi.</v>
       </c>
       <c r="O13" t="str">
-        <v>Pemadaman apabila terdapat gangguan N–1–1.</v>
+        <v>Pemadaman apabila terdapat gangguan N-1-1.</v>
       </c>
       <c r="P13" t="str">
-        <v>Pemeliharaan mengikuti jadwal KTT industri.</v>
+        <v>Pemeliharaan mengikuti jadwal KTT.</v>
       </c>
       <c r="Q13" t="str">
-        <v>Double phi transmisi 150 kV COD 2030.</v>
+        <v>Double phi COD 2030.</v>
       </c>
     </row>
     <row r="14">
@@ -3335,13 +2733,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Gardu Induk MCCI5 (150 kV)</v>
+        <v>GI Mitsubishi Chemical (MCCI)</v>
       </c>
       <c r="C14" t="str">
         <v>MCCI5</v>
       </c>
       <c r="D14" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E14" t="str">
         <v>Normal</v>
@@ -3371,13 +2769,13 @@
         <v>JBB</v>
       </c>
       <c r="N14" t="str">
-        <v>Ruas Penghantar Suralaya–MCCI–Cilegon masih single phi.</v>
+        <v>Ruas Penghantar Suralaya-MCCI-Cilegon masih single phi.</v>
       </c>
       <c r="O14" t="str">
-        <v>Pemadaman apabila trip saat pemeliharaan KTT.</v>
+        <v>Pemadaman apabila gangguan.</v>
       </c>
       <c r="P14" t="str">
-        <v>Penyesuaian jadwal pemeliharaan dari KTT.</v>
+        <v>Penyesuaian jadwal pemeliharaan.</v>
       </c>
       <c r="Q14" t="str">
         <v>Usulan double phi ruas Suralaya s.d Cilegon Lama.</v>
@@ -3388,13 +2786,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Gardu Induk CLGON (150 kV)</v>
+        <v>GI Cilegon Lama</v>
       </c>
       <c r="C15" t="str">
         <v>CLGON</v>
       </c>
       <c r="D15" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E15" t="str">
         <v>Normal</v>
@@ -3424,7 +2822,7 @@
         <v>JBB</v>
       </c>
       <c r="N15" t="str">
-        <v>Gardu Induk Cilegon Lama (Menerima double circuit dari CLBRU, serta loop dari MCCI5 dan MTSUI)</v>
+        <v>Gardu Induk Cilegon Lama</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -3441,13 +2839,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Gardu Induk MTSUI (150 kV)</v>
+        <v>GI Mitsui (MTSUI)</v>
       </c>
       <c r="C16" t="str">
         <v>MTSUI</v>
       </c>
       <c r="D16" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="E16" t="str">
         <v>Normal</v>
@@ -3477,16 +2875,16 @@
         <v>JBB</v>
       </c>
       <c r="N16" t="str">
-        <v>Ruas Peni–Mitsui–Cilegon masih single phi (Tier 3).</v>
+        <v>Ruas Mitsui-Cilegon single phi</v>
       </c>
       <c r="O16" t="str">
-        <v>Terjadi pemadaman apabila trip N-1.</v>
+        <v/>
       </c>
       <c r="P16" t="str">
-        <v>Pengaturan konfigurasi jaringan.</v>
+        <v/>
       </c>
       <c r="Q16" t="str">
-        <v>Double phi ruas Suralaya s.d Cilegon Lama.</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -3494,13 +2892,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>KTT SLFDO-1</v>
+        <v>Konsumen KTT SLFDO-1 (78 MVA)</v>
       </c>
       <c r="C17" t="str">
         <v>KTT SLFDO-1</v>
       </c>
       <c r="D17" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E17" t="str">
         <v>Normal</v>
@@ -3530,7 +2928,7 @@
         <v>JBB</v>
       </c>
       <c r="N17" t="str">
-        <v>Konsumen Tegangan Tinggi SLFDO-1 (78 MVA)</v>
+        <v>Konsumen Tegangan Tinggi SLFDO-1</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -3547,13 +2945,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>KTT SLFDO-2</v>
+        <v>Konsumen KTT SLFDO-2 (30 MVA)</v>
       </c>
       <c r="C18" t="str">
         <v>KTT SLFDO-2</v>
       </c>
       <c r="D18" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E18" t="str">
         <v>Normal</v>
@@ -3583,7 +2981,7 @@
         <v>JBB</v>
       </c>
       <c r="N18" t="str">
-        <v>Konsumen Tegangan Tinggi SLFDO-2 (30 MVA)</v>
+        <v>Konsumen Tegangan Tinggi SLFDO-2</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -3600,13 +2998,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>KTT PENDO</v>
+        <v>Konsumen KTT PENDO (35 MVA)</v>
       </c>
       <c r="C19" t="str">
         <v>KTT PENDO</v>
       </c>
       <c r="D19" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E19" t="str">
         <v>Normal</v>
@@ -3636,7 +3034,7 @@
         <v>JBB</v>
       </c>
       <c r="N19" t="str">
-        <v>Konsumen Tegangan Tinggi PENDO (35 MVA)</v>
+        <v>Konsumen Tegangan Tinggi PENDO</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -3653,13 +3051,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>KTT PENI</v>
+        <v>Konsumen KTT PENI (40 MVA)</v>
       </c>
       <c r="C20" t="str">
         <v>KTT PENI</v>
       </c>
       <c r="D20" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E20" t="str">
         <v>Normal</v>
@@ -3689,16 +3087,16 @@
         <v>JBB</v>
       </c>
       <c r="N20" t="str">
-        <v>Konsumen Tegangan Tinggi PENI Chandra Asri (40 MVA, Memiliki Kerawanan #3)</v>
+        <v>Konsumen Tegangan Tinggi PENI Chandra Asri</v>
       </c>
       <c r="O20" t="str">
-        <v>Potensi kendala operasional saat gangguan ruas single phi.</v>
+        <v/>
       </c>
       <c r="P20" t="str">
-        <v>Jadwal pemeliharaan selaras dengan turn-around pabrik.</v>
+        <v/>
       </c>
       <c r="Q20" t="str">
-        <v>Usulan perkuatan sistem suplai transmisi.</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -3706,13 +3104,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>KTT LCI</v>
+        <v>Konsumen KTT LCI (115 MVA)</v>
       </c>
       <c r="C21" t="str">
         <v>KTT LCI</v>
       </c>
       <c r="D21" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E21" t="str">
         <v>Normal</v>
@@ -3742,7 +3140,7 @@
         <v>JBB</v>
       </c>
       <c r="N21" t="str">
-        <v>Konsumen KTT LCI (115 MVA, Disuplai 2 Sirkit dengan 2 PMT CB)</v>
+        <v>Konsumen KTT LCI</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -3759,13 +3157,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>KTT MCCI</v>
+        <v>Konsumen KTT MCCI (40 MVA)</v>
       </c>
       <c r="C22" t="str">
         <v>KTT MCCI</v>
       </c>
       <c r="D22" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E22" t="str">
         <v>Normal</v>
@@ -3795,7 +3193,7 @@
         <v>JBB</v>
       </c>
       <c r="N22" t="str">
-        <v>Konsumen Tegangan Tinggi MCCI (40 MVA)</v>
+        <v>Konsumen KTT MCCI</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -3812,13 +3210,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>KTT MTSUI</v>
+        <v>Konsumen KTT MTSUI (31 MVA)</v>
       </c>
       <c r="C23" t="str">
         <v>KTT MTSUI</v>
       </c>
       <c r="D23" t="str">
-        <v>trafo_distribusi</v>
+        <v>Beban</v>
       </c>
       <c r="E23" t="str">
         <v>Normal</v>
@@ -3848,7 +3246,7 @@
         <v>JBB</v>
       </c>
       <c r="N23" t="str">
-        <v>Konsumen Tegangan Tinggi Mitsui (31 MVA, Terhubung ke GI MTSUI)</v>
+        <v>Konsumen KTT Mitsui</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -3865,25 +3263,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Trafo Distribusi SRLYA</v>
+        <v>Konsumen KSTEL (Krakatau Steel)</v>
       </c>
       <c r="C24" t="str">
-        <v>Trafo SRLYA</v>
+        <v>KSTEL</v>
       </c>
       <c r="D24" t="str">
-        <v>trafo_distribusi</v>
+        <v>Busbar</v>
       </c>
       <c r="E24" t="str">
         <v>Normal</v>
       </c>
       <c r="F24" t="str">
-        <v>60 MVA</v>
+        <v/>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="str">
-        <v>150/20 kV</v>
+        <v>150 kV</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -3901,7 +3299,7 @@
         <v>JBB</v>
       </c>
       <c r="N24" t="str">
-        <v>Trafo distribusi lokal 150/20 kV Suralaya</v>
+        <v>Konsumen KSTEL (Krakatau Steel)</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -3918,25 +3316,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Trafo Distribusi CLBRU</v>
+        <v>Konsumen POSCO (Krakatau POSCO)</v>
       </c>
       <c r="C25" t="str">
-        <v>Trafo CLBRU</v>
+        <v>POSCO</v>
       </c>
       <c r="D25" t="str">
-        <v>trafo_distribusi</v>
+        <v>Busbar</v>
       </c>
       <c r="E25" t="str">
         <v>Normal</v>
       </c>
       <c r="F25" t="str">
-        <v>60 MVA</v>
+        <v/>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" t="str">
-        <v>150/20 kV</v>
+        <v>150 kV</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -3954,7 +3352,7 @@
         <v>JBB</v>
       </c>
       <c r="N25" t="str">
-        <v>Trafo distribusi lokal 150/20 kV Cilegon Baru</v>
+        <v>Konsumen Krakatau POSCO</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -3963,185 +3361,19 @@
         <v/>
       </c>
       <c r="Q25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Trafo Distribusi CLGON</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Trafo CLGON</v>
-      </c>
-      <c r="D26" t="str">
-        <v>trafo_distribusi</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F26" t="str">
-        <v>60 MVA</v>
-      </c>
-      <c r="G26">
-        <v>3</v>
-      </c>
-      <c r="H26" t="str">
-        <v>150/20 kV</v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v>Banten</v>
-      </c>
-      <c r="M26" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="N26" t="str">
-        <v>Trafo distribusi lokal 150/20 kV Cilegon Lama</v>
-      </c>
-      <c r="O26" t="str">
-        <v/>
-      </c>
-      <c r="P26" t="str">
-        <v/>
-      </c>
-      <c r="Q26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>KSTEL</v>
-      </c>
-      <c r="C27" t="str">
-        <v>KSTEL</v>
-      </c>
-      <c r="D27" t="str">
-        <v>cb</v>
-      </c>
-      <c r="E27" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27">
-        <v>3</v>
-      </c>
-      <c r="H27" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v>Banten</v>
-      </c>
-      <c r="M27" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="N27" t="str">
-        <v>Bay Rencana Konsumen Krakatau Steel (KSTEL) Garis Putus-putus</v>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-      <c r="P27" t="str">
-        <v/>
-      </c>
-      <c r="Q27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>POSCO</v>
-      </c>
-      <c r="C28" t="str">
-        <v>POSCO</v>
-      </c>
-      <c r="D28" t="str">
-        <v>cb</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28">
-        <v>3</v>
-      </c>
-      <c r="H28" t="str">
-        <v>150 kV</v>
-      </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v>Normal</v>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v>Banten</v>
-      </c>
-      <c r="M28" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="N28" t="str">
-        <v>Bay Rencana Konsumen Krakatau Posco (POSCO) Garis Putus-putus</v>
-      </c>
-      <c r="O28" t="str">
-        <v/>
-      </c>
-      <c r="P28" t="str">
-        <v/>
-      </c>
-      <c r="Q28" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q28"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q25"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="48.83203125" customWidth="1"/>
-    <col min="4" max="4" width="55.83203125" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4162,127 +3394,150 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1. Pembangkit / Generator</v>
+        <v>Peralatan (1)</v>
       </c>
       <c r="B2" t="str">
-        <v>generator</v>
+        <v>Generator / Pembangkit</v>
       </c>
       <c r="C2" t="str">
-        <v>Lingkaran Hijau + Simbol Gelombang AC (~)</v>
+        <v>Lingkaran Hijau dengan Gelombang Sinus AC (~)</v>
       </c>
       <c r="D2" t="str">
-        <v>Digunakan untuk merepresentasikan sumber daya pembangkitan (PLTU, PLTGU, PLTA, dll). Pada diagram terletak di bagian paling atas (Unit 3).</v>
+        <v>Titik hulu pembangkit listrik utama (PLTU, PLTA, PLTG, PLTGU).</v>
       </c>
       <c r="E2" t="str">
-        <v>PLTU Suralaya Unit 3, PLTGU Muara Karang Unit 1-3</v>
+        <v>PLTU Suralaya Unit 3 (600 MW)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2. Trafo Generator (GSUT)</v>
+        <v>Peralatan (2)</v>
       </c>
       <c r="B3" t="str">
-        <v>trafo_generator</v>
+        <v>Trafo Generator (GSUT)</v>
       </c>
       <c r="C3" t="str">
-        <v>Dua Cincin Bertaut: Atas Hijau (Generator), Bawah Merah (Tegangan Tinggi)</v>
+        <v>2 Lingkaran Interlocking (Atas: Hijau sisi Gen, Bawah: Merah sisi GI)</v>
       </c>
       <c r="D3" t="str">
-        <v>Digunakan untuk menaikkan tegangan dari generator pembangkit ke tegangan sistem transmisi (Generator Step-Up Transformer / GSUT).</v>
+        <v>Trafo penaik tegangan generator (Generator Step-Up) dari 15-20 kV ke tegangan tinggi GI (150/500 kV).</v>
       </c>
       <c r="E3" t="str">
-        <v>Trafo Step-Up PLTU Unit 3 ke Busbar 150 kV SRLYA</v>
+        <v>Bay Pembangkit ke Busbar GI</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3. Circuit Breaker (PMT)</v>
+        <v>Switching (3)</v>
       </c>
       <c r="B4" t="str">
-        <v>cb</v>
+        <v>CB / PMT (Pemutus Tenaga)</v>
       </c>
       <c r="C4" t="str">
-        <v>Balok Persegi Merah Solid pada Jalur Penghantar</v>
+        <v>Balok / Persegi Panjang Solid Merah Tegak dengan garis terminal</v>
       </c>
       <c r="D4" t="str">
-        <v>Pemutus Tenaga (PMT / Circuit Breaker) yang diletakkan pada bay pengirim maupun penerima GI ke GI untuk memutus arus gangguan.</v>
+        <v>Circuit Breaker pada bay pengirim dan penerima GI ke GI untuk memutus beban dan gangguan arus pendek.</v>
       </c>
       <c r="E4" t="str">
-        <v>Semua bay outgoing/incoming SUTT 150 kV, bay trafo, dan bay IBT</v>
+        <v>Bay Line, Bay IBT, Bay Trafo, Bay Generator</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4. Interbus Transformer (IBT)</v>
+        <v>Peralatan (4)</v>
       </c>
       <c r="B5" t="str">
-        <v>ibt</v>
+        <v>IBT (Interbus Transformer)</v>
       </c>
       <c r="C5" t="str">
-        <v>Tiga Cincin Bertaut: Atas Biru (500 kV), Kiri Merah (150 kV), Kanan Kuning (Tertiary 33/20 kV)</v>
+        <v>3 Lingkaran Bertumpuk (Atas Biru 500kV, Kiri Merah 150kV, Kanan Kuning 33kV)</v>
       </c>
       <c r="D5" t="str">
-        <v>Transformator Daya Besar (3 Winding) penghubung antar grid tegangan ekstra tinggi 500 kV atau 275 kV ke tegangan transmisi 150 kV.</v>
+        <v>Trafo interkoneksi sistem transmisi tegangan ekstra tinggi (500/150 kV atau 275/150 kV).</v>
       </c>
       <c r="E5" t="str">
-        <v>IBT 1 Suralaya (500/150 kV), IBT 2 Suralaya Baru, IBT 4 Cilegon Baru</v>
+        <v>IBT 1 &amp; 2 Suralaya (250 MVA), IBT 4 Cilegon (500 MVA)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5. Trafo Distribusi / KTT</v>
+        <v>Peralatan (5)</v>
       </c>
       <c r="B6" t="str">
-        <v>trafo_distribusi</v>
+        <v>Trafo Distribusi</v>
       </c>
       <c r="C6" t="str">
-        <v>Dua Cincin Bertaut: Atas Merah (150 kV), Bawah Kuning (20 kV / 70 kV)</v>
+        <v>2 Lingkaran Interlocking (Atas: Merah 150kV, Bawah: Kuning 20kV / 70kV)</v>
       </c>
       <c r="D6" t="str">
-        <v>Transformator penurun tegangan dari transmisi 150 kV ke tegangan menengah 20 kV (atau 70 kV) untuk melayani gardu distribusi &amp; konsumen tegangan tinggi (KTT).</v>
+        <v>Trafo step-down daya di Gardu Induk yang menurunkan tegangan dari 150 kV ke 70 kV atau 20 kV.</v>
       </c>
       <c r="E6" t="str">
-        <v>Trafo KTT SLFDO-1 (78 MVA), KTT PENI (40 MVA), KTT LCI (115 MVA), KTT MTSUI</v>
+        <v>Trafo 150/20 kV GI Distribusi / Feeder KTT</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6. Busbar (Rel Konduktor)</v>
+        <v>Peralatan (6)</v>
       </c>
       <c r="B7" t="str">
-        <v>busbar</v>
+        <v>Busbar</v>
       </c>
       <c r="C7" t="str">
-        <v>Garis Horisontal Tebal: Biru (500 kV) atau Merah (150 kV)</v>
+        <v>Batang Rel Horizontal Tebal (Cyan/Biru)</v>
       </c>
       <c r="D7" t="str">
-        <v>Rel konduktor pengumpul daya listrik di gardu induk. Dapat diset 'Normal' atau 'Panjang (Wide Busbar)' untuk membentang di atas beberapa bay.</v>
+        <v>Batang konduktor utama di Gardu Induk (GI / GITET) yang mengumpulkan dan membagikan daya listrik.</v>
       </c>
       <c r="E7" t="str">
-        <v>Rel 500 kV Suralaya Baru, Rel 150 kV SRLYA (Wide Busbar), Rel 150 kV CLBRU</v>
+        <v>Suralaya Baru (500 kV), GI SRLYA 150 kV, GI CLBRU 150 kV</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Peralatan (7)</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Beban</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Segitiga Terbalik (∇) Kuning Emas dengan terminal bulatan di atas</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Simbol resmi beban listrik konsumen industri KTT (Konsumen Tegangan Tinggi) atau feeder beban.</v>
+      </c>
+      <c r="E8" t="str">
+        <v>KTT SLFDO-1 (78 MVA), KTT PENI (40 MVA), KTT LCI (115 MVA)</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Peralatan (8)</v>
+      </c>
+      <c r="B9" t="str">
+        <v>PHT (Penghantar)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Kapsul Saluran Transmisi dengan dua bulatan terminal di ujung</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Saluran udara/kabel transmisi tenaga listrik penghubung antar gardu induk.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>PHT Suralaya - Salira Indah, PHT Suralaya - PENI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="24.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-    <col min="7" max="7" width="40.83203125" customWidth="1"/>
-    <col min="8" max="8" width="40.83203125" customWidth="1"/>
-    <col min="9" max="9" width="40.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4295,21 +3550,18 @@
         <v>Subsistem</v>
       </c>
       <c r="D1" t="str">
-        <v>Peralatan Terdampak</v>
+        <v>UIT</v>
       </c>
       <c r="E1" t="str">
-        <v>UIT</v>
+        <v>Kondisi / Permasalahan</v>
       </c>
       <c r="F1" t="str">
-        <v>Kondisi / Permasalahan</v>
+        <v>Dampak</v>
       </c>
       <c r="G1" t="str">
-        <v>Dampak</v>
+        <v>Mitigasi</v>
       </c>
       <c r="H1" t="str">
-        <v>Mitigasi</v>
-      </c>
-      <c r="I1" t="str">
         <v>Usulan / Solusi</v>
       </c>
     </row>
@@ -4321,30 +3573,27 @@
         <v>1&amp;2</v>
       </c>
       <c r="C2" t="str">
-        <v>Suralaya - Cilegon</v>
+        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
       </c>
       <c r="D2" t="str">
-        <v>IBT 1 Suralaya &amp; IBT 2 Suralaya Baru (500/150 kV)</v>
+        <v>JBB</v>
       </c>
       <c r="E2" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="F2" t="str">
         <v>Pembebanan IBT–1,2 Suralaya tidak memenuhi kriteria N–1 saat PLTU Suralaya unit–3 tidak beroperasi dan IBT–4 Cilegon masuk sub sistem Cilegon.</v>
       </c>
-      <c r="G2" t="str" xml:space="preserve">
+      <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan IBT sulit dilakukan.
 2. Pertumbuhan beban menjadi terhambat.
 3. Terjadi pemadaman apabila trip salah satu IBT di Suralaya.</v>
       </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025).
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025).
+3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit–3 beroperasi.</v>
+      </c>
       <c r="H2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW.
-2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan target total 137 MW.
-3. Pemeliharaan IBT saat beban rendah dan Unit 3 beroperasi.</v>
-      </c>
-      <c r="I2" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025/2026.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2025.</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -4355,27 +3604,26 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>Suralaya - Cilegon</v>
+        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
       </c>
       <c r="D3" t="str">
-        <v>IBT 4 Cilegon Baru (500/150 kV)</v>
+        <v>JBB</v>
       </c>
       <c r="E3" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="F3" t="str">
         <v>Daya Mampu Pasok IBT Suralaya dan Cilegon tidak sama (IBT #1,2 Suralaya 250 MVA sedangkan IBT #4 Cilegon 500 MVA).</v>
       </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
+2. Kondisi N–1–1 (IBT Suralaya dan IBT Cilegon) berdampak overload pada IBT Suralaya yang beroperasi.</v>
+      </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Ketidakseimbangan beban antara IBT Suralaya dan IBT Cilegon.
-2. Kondisi N–1–1 berdampak overload pada IBT Suralaya yang beroperasi.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Optimalisasi transfer trip dan defense scheme antar GI.</v>
-      </c>
-      <c r="I3" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Sudah terpasang DS OLS IBT 1,2 Suralaya dengan target total sebesar 102 MW (Berdasarkan buku DS Tahun 2025).
+2. Rencana penambahan target DS OLS SS Suralaya 1,2 dengan total target sebesar 137 MW (Berdasarkan buku DS Tahun 2025).
+3. Pemeliharaan IBT saat beban rendah dan pada saat PLTU Suralaya Unit–3 beroperasi.</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Pendek :
-Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA.</v>
+Uprating IBT–1 &amp; 2 Suralaya dari 250 MVA menjadi 500 MVA. Berdasarkan RUPTL 2025 – 2034, COD di Tahun 2026.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -4386,33 +3634,30 @@
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>Suralaya - Cilegon</v>
+        <v>Subsistem Suralaya Unit #3 - Suralaya 1,2 – Cilegon 4</v>
       </c>
       <c r="D4" t="str">
-        <v>Ruas SUTT Suralaya–PENI, Suralaya–MCCI, MCCI–Cilegon, PENI–Mitsui–Cilegon</v>
+        <v>JBB</v>
       </c>
       <c r="E4" t="str">
-        <v>JBB</v>
-      </c>
-      <c r="F4" t="str">
         <v>Ruas Penghantar Suralaya–MCCI–Cilegon dan Suralaya–Peni–Mitsui–Cilegon masih single phi.</v>
       </c>
-      <c r="G4" t="str" xml:space="preserve">
+      <c r="F4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan Penghantar menjadi sulit dilakukan.
 2. Terjadi pemadaman apabila terdapat gangguan N–1–1.</v>
       </c>
-      <c r="H4" t="str" xml:space="preserve">
+      <c r="G4" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Pemeliharaan Penghantar menyesuaikan jadwal dari KTT.
 2. Pengaturan konfigurasi jaringan saat pemeliharaan untuk mengurangi dampak padam.</v>
       </c>
-      <c r="I4" t="str" xml:space="preserve">
+      <c r="H4" t="str" xml:space="preserve">
         <v xml:space="preserve">Jangka Menengah :
 Usulan Double phi pada ruas Suralaya s.d Cilegon Lama (Kajian belum ada). Diusulkan COD Tahun 2030.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
+++ b/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -23,13 +23,26 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -44,8 +57,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,12 +471,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama Penghantar</t>
         </is>
@@ -477,7 +491,7 @@
           <t>Tipe Simbol SLD</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Dari GI</t>
         </is>
@@ -487,12 +501,12 @@
           <t>Tipe Simbol Dari GI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tier Dari GI</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ke GI</t>
         </is>
@@ -502,12 +516,12 @@
           <t>Tipe Simbol Ke GI</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Tier Ke GI</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Tegangan</t>
         </is>
@@ -527,7 +541,7 @@
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Tingkat Kerawanan</t>
         </is>
@@ -2468,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM25"/>
+  <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="18" max="18"/>
@@ -2482,17 +2496,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Nama Asset / GI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Kode Singkatan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Tipe Simbol SLD</t>
         </is>
@@ -2507,12 +2521,12 @@
           <t>Kapasitas (MVA / MW)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Tier (Mulai 0)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Tegangan</t>
         </is>
@@ -2522,12 +2536,12 @@
           <t>No IBT</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
@@ -4457,12 +4471,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
@@ -4477,7 +4491,7 @@
           <t>UIT</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kondisi / Permasalahan</t>
         </is>

--- a/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
+++ b/peta-kerawanan/public/template_kerawanan_subsistem_suralaya_cilegon.xlsx
@@ -2190,7 +2190,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Suralaya - Cilegon Baru</v>
+        <v>Suralaya Baru - Cilegon Baru</v>
       </c>
       <c r="D24" t="str">
         <v>PHT</v>
@@ -2199,7 +2199,7 @@
         <v>PHT</v>
       </c>
       <c r="F24" t="str">
-        <v>Suralaya</v>
+        <v>Suralaya Baru</v>
       </c>
       <c r="G24" t="str">
         <v>Busbar</v>
@@ -2267,7 +2267,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Suralaya - Cilegon Baru</v>
+        <v>Suralaya Baru - Cilegon Baru</v>
       </c>
       <c r="D25" t="str">
         <v>PHT</v>
@@ -2276,7 +2276,7 @@
         <v>PHT</v>
       </c>
       <c r="F25" t="str">
-        <v>Suralaya</v>
+        <v>Suralaya Baru</v>
       </c>
       <c r="G25" t="str">
         <v>Busbar</v>
